--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25097300</v>
+        <v>25475300</v>
       </c>
       <c r="E8" s="3">
-        <v>12669100</v>
+        <v>12859900</v>
       </c>
       <c r="F8" s="3">
-        <v>12304200</v>
+        <v>12489500</v>
       </c>
       <c r="G8" s="3">
-        <v>16310300</v>
+        <v>16555900</v>
       </c>
       <c r="H8" s="3">
-        <v>16526300</v>
+        <v>16775200</v>
       </c>
       <c r="I8" s="3">
-        <v>14380900</v>
+        <v>14597400</v>
       </c>
       <c r="J8" s="3">
-        <v>12695900</v>
+        <v>12887100</v>
       </c>
       <c r="K8" s="3">
         <v>13732100</v>
@@ -993,16 +993,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-1298300</v>
+        <v>-1317900</v>
       </c>
       <c r="E15" s="3">
-        <v>-1291400</v>
+        <v>-1310800</v>
       </c>
       <c r="F15" s="3">
-        <v>-1210100</v>
+        <v>-1228300</v>
       </c>
       <c r="G15" s="3">
-        <v>-1200300</v>
+        <v>-1218400</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>5</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14836600</v>
+        <v>15060100</v>
       </c>
       <c r="E17" s="3">
-        <v>4156900</v>
+        <v>4219500</v>
       </c>
       <c r="F17" s="3">
-        <v>5685600</v>
+        <v>5771200</v>
       </c>
       <c r="G17" s="3">
-        <v>8919100</v>
+        <v>9053400</v>
       </c>
       <c r="H17" s="3">
-        <v>8274300</v>
+        <v>8398900</v>
       </c>
       <c r="I17" s="3">
-        <v>5703700</v>
+        <v>5789600</v>
       </c>
       <c r="J17" s="3">
-        <v>4668000</v>
+        <v>4738300</v>
       </c>
       <c r="K17" s="3">
         <v>3929800</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10260700</v>
+        <v>10415200</v>
       </c>
       <c r="E18" s="3">
-        <v>8512200</v>
+        <v>8640400</v>
       </c>
       <c r="F18" s="3">
-        <v>6618600</v>
+        <v>6718300</v>
       </c>
       <c r="G18" s="3">
-        <v>7391200</v>
+        <v>7502500</v>
       </c>
       <c r="H18" s="3">
-        <v>8252000</v>
+        <v>8376300</v>
       </c>
       <c r="I18" s="3">
-        <v>8677100</v>
+        <v>8807800</v>
       </c>
       <c r="J18" s="3">
-        <v>8027900</v>
+        <v>8148800</v>
       </c>
       <c r="K18" s="3">
         <v>9802300</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2966800</v>
+        <v>-3011500</v>
       </c>
       <c r="E20" s="3">
-        <v>-2339700</v>
+        <v>-2375000</v>
       </c>
       <c r="F20" s="3">
-        <v>-2155000</v>
+        <v>-2187400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1490600</v>
+        <v>-1513000</v>
       </c>
       <c r="H20" s="3">
-        <v>-791400</v>
+        <v>-803400</v>
       </c>
       <c r="I20" s="3">
-        <v>-1314400</v>
+        <v>-1334200</v>
       </c>
       <c r="J20" s="3">
-        <v>-1525300</v>
+        <v>-1548300</v>
       </c>
       <c r="K20" s="3">
         <v>-2598000</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9064900</v>
+        <v>9217600</v>
       </c>
       <c r="E21" s="3">
-        <v>7771500</v>
+        <v>7903200</v>
       </c>
       <c r="F21" s="3">
-        <v>5965300</v>
+        <v>6068900</v>
       </c>
       <c r="G21" s="3">
-        <v>7399300</v>
+        <v>7524400</v>
       </c>
       <c r="H21" s="3">
-        <v>9410000</v>
+        <v>9569600</v>
       </c>
       <c r="I21" s="3">
-        <v>9390400</v>
+        <v>9550400</v>
       </c>
       <c r="J21" s="3">
-        <v>8513700</v>
+        <v>8660400</v>
       </c>
       <c r="K21" s="3">
         <v>9140900</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7293900</v>
+        <v>7403700</v>
       </c>
       <c r="E23" s="3">
-        <v>6172500</v>
+        <v>6265400</v>
       </c>
       <c r="F23" s="3">
-        <v>4463700</v>
+        <v>4530900</v>
       </c>
       <c r="G23" s="3">
-        <v>5900600</v>
+        <v>5989500</v>
       </c>
       <c r="H23" s="3">
-        <v>7460600</v>
+        <v>7572900</v>
       </c>
       <c r="I23" s="3">
-        <v>7362800</v>
+        <v>7473600</v>
       </c>
       <c r="J23" s="3">
-        <v>6502600</v>
+        <v>6600500</v>
       </c>
       <c r="K23" s="3">
         <v>7204200</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1873500</v>
+        <v>1901700</v>
       </c>
       <c r="E24" s="3">
-        <v>1424500</v>
+        <v>1446000</v>
       </c>
       <c r="F24" s="3">
-        <v>1038100</v>
+        <v>1053800</v>
       </c>
       <c r="G24" s="3">
-        <v>1113400</v>
+        <v>1130200</v>
       </c>
       <c r="H24" s="3">
-        <v>2200700</v>
+        <v>2233800</v>
       </c>
       <c r="I24" s="3">
-        <v>1796300</v>
+        <v>1823300</v>
       </c>
       <c r="J24" s="3">
-        <v>1135100</v>
+        <v>1152200</v>
       </c>
       <c r="K24" s="3">
         <v>1654100</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>5420400</v>
+        <v>5502000</v>
       </c>
       <c r="E26" s="3">
-        <v>4748000</v>
+        <v>4819500</v>
       </c>
       <c r="F26" s="3">
-        <v>3425500</v>
+        <v>3477100</v>
       </c>
       <c r="G26" s="3">
-        <v>4787200</v>
+        <v>4859300</v>
       </c>
       <c r="H26" s="3">
-        <v>5259900</v>
+        <v>5339100</v>
       </c>
       <c r="I26" s="3">
-        <v>5566500</v>
+        <v>5650300</v>
       </c>
       <c r="J26" s="3">
-        <v>5367500</v>
+        <v>5448300</v>
       </c>
       <c r="K26" s="3">
         <v>5550200</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5350800</v>
+        <v>5431400</v>
       </c>
       <c r="E27" s="3">
-        <v>4692000</v>
+        <v>4762700</v>
       </c>
       <c r="F27" s="3">
-        <v>3405100</v>
+        <v>3456400</v>
       </c>
       <c r="G27" s="3">
-        <v>4673800</v>
+        <v>4744200</v>
       </c>
       <c r="H27" s="3">
-        <v>4825200</v>
+        <v>4897800</v>
       </c>
       <c r="I27" s="3">
-        <v>4876200</v>
+        <v>4949600</v>
       </c>
       <c r="J27" s="3">
-        <v>4691300</v>
+        <v>4761900</v>
       </c>
       <c r="K27" s="3">
         <v>4753100</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2966800</v>
+        <v>3011500</v>
       </c>
       <c r="E32" s="3">
-        <v>2339700</v>
+        <v>2375000</v>
       </c>
       <c r="F32" s="3">
-        <v>2155000</v>
+        <v>2187400</v>
       </c>
       <c r="G32" s="3">
-        <v>1490600</v>
+        <v>1513000</v>
       </c>
       <c r="H32" s="3">
-        <v>791400</v>
+        <v>803400</v>
       </c>
       <c r="I32" s="3">
-        <v>1314400</v>
+        <v>1334200</v>
       </c>
       <c r="J32" s="3">
-        <v>1525300</v>
+        <v>1548300</v>
       </c>
       <c r="K32" s="3">
         <v>2598000</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5350800</v>
+        <v>5431400</v>
       </c>
       <c r="E33" s="3">
-        <v>4692000</v>
+        <v>4762700</v>
       </c>
       <c r="F33" s="3">
-        <v>3405100</v>
+        <v>3456400</v>
       </c>
       <c r="G33" s="3">
-        <v>4673800</v>
+        <v>4744200</v>
       </c>
       <c r="H33" s="3">
-        <v>4825200</v>
+        <v>4897800</v>
       </c>
       <c r="I33" s="3">
-        <v>4876200</v>
+        <v>4949600</v>
       </c>
       <c r="J33" s="3">
-        <v>4691300</v>
+        <v>4761900</v>
       </c>
       <c r="K33" s="3">
         <v>4753100</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>5350800</v>
+        <v>5431400</v>
       </c>
       <c r="E35" s="3">
-        <v>4692000</v>
+        <v>4762700</v>
       </c>
       <c r="F35" s="3">
-        <v>3405100</v>
+        <v>3456400</v>
       </c>
       <c r="G35" s="3">
-        <v>4673800</v>
+        <v>4744200</v>
       </c>
       <c r="H35" s="3">
-        <v>4825200</v>
+        <v>4897800</v>
       </c>
       <c r="I35" s="3">
-        <v>4876200</v>
+        <v>4949600</v>
       </c>
       <c r="J35" s="3">
-        <v>4691300</v>
+        <v>4761900</v>
       </c>
       <c r="K35" s="3">
         <v>4753100</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>504069000</v>
+        <v>511660000</v>
       </c>
       <c r="E41" s="3">
-        <v>496620000</v>
+        <v>504099000</v>
       </c>
       <c r="F41" s="3">
-        <v>481857000</v>
+        <v>489114000</v>
       </c>
       <c r="G41" s="3">
-        <v>410143000</v>
+        <v>416320000</v>
       </c>
       <c r="H41" s="3">
-        <v>381211000</v>
+        <v>386952000</v>
       </c>
       <c r="I41" s="3">
-        <v>356784000</v>
+        <v>362158000</v>
       </c>
       <c r="J41" s="3">
-        <v>311187000</v>
+        <v>315874000</v>
       </c>
       <c r="K41" s="3">
         <v>314501000</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>221110000</v>
+        <v>224440000</v>
       </c>
       <c r="E42" s="3">
-        <v>193786000</v>
+        <v>196704000</v>
       </c>
       <c r="F42" s="3">
-        <v>181894000</v>
+        <v>184633000</v>
       </c>
       <c r="G42" s="3">
-        <v>190167000</v>
+        <v>193031000</v>
       </c>
       <c r="H42" s="3">
-        <v>163579000</v>
+        <v>166042000</v>
       </c>
       <c r="I42" s="3">
-        <v>156239000</v>
+        <v>158592000</v>
       </c>
       <c r="J42" s="3">
-        <v>162229000</v>
+        <v>164672000</v>
       </c>
       <c r="K42" s="3">
         <v>174560000</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8954900</v>
+        <v>9089800</v>
       </c>
       <c r="E47" s="3">
-        <v>7881500</v>
+        <v>8000200</v>
       </c>
       <c r="F47" s="3">
-        <v>6385600</v>
+        <v>6481700</v>
       </c>
       <c r="G47" s="3">
-        <v>6272400</v>
+        <v>6366900</v>
       </c>
       <c r="H47" s="3">
-        <v>6479600</v>
+        <v>6577200</v>
       </c>
       <c r="I47" s="3">
-        <v>4536100</v>
+        <v>4604400</v>
       </c>
       <c r="J47" s="3">
-        <v>4014200</v>
+        <v>4074700</v>
       </c>
       <c r="K47" s="3">
         <v>4486600</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>9923700</v>
+        <v>10073100</v>
       </c>
       <c r="E48" s="3">
-        <v>9676200</v>
+        <v>9821900</v>
       </c>
       <c r="F48" s="3">
-        <v>9687700</v>
+        <v>9833600</v>
       </c>
       <c r="G48" s="3">
-        <v>9630100</v>
+        <v>9775200</v>
       </c>
       <c r="H48" s="3">
-        <v>9991200</v>
+        <v>10141700</v>
       </c>
       <c r="I48" s="3">
-        <v>23074900</v>
+        <v>23422400</v>
       </c>
       <c r="J48" s="3">
-        <v>20594900</v>
+        <v>20905100</v>
       </c>
       <c r="K48" s="3">
         <v>21457800</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>5961700</v>
+        <v>6051500</v>
       </c>
       <c r="E49" s="3">
-        <v>5968100</v>
+        <v>6058000</v>
       </c>
       <c r="F49" s="3">
-        <v>4905400</v>
+        <v>4979200</v>
       </c>
       <c r="G49" s="3">
-        <v>5003800</v>
+        <v>5079100</v>
       </c>
       <c r="H49" s="3">
-        <v>5107700</v>
+        <v>5184600</v>
       </c>
       <c r="I49" s="3">
-        <v>5747500</v>
+        <v>5834000</v>
       </c>
       <c r="J49" s="3">
-        <v>6284800</v>
+        <v>6379500</v>
       </c>
       <c r="K49" s="3">
         <v>6455200</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5170800</v>
+        <v>5248700</v>
       </c>
       <c r="E52" s="3">
-        <v>4580000</v>
+        <v>4649000</v>
       </c>
       <c r="F52" s="3">
-        <v>3953300</v>
+        <v>4012800</v>
       </c>
       <c r="G52" s="3">
-        <v>1705700</v>
+        <v>1731400</v>
       </c>
       <c r="H52" s="3">
-        <v>2454700</v>
+        <v>2491600</v>
       </c>
       <c r="I52" s="3">
-        <v>2729200</v>
+        <v>2770300</v>
       </c>
       <c r="J52" s="3">
-        <v>2509400</v>
+        <v>2547200</v>
       </c>
       <c r="K52" s="3">
         <v>2418900</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1795650000</v>
+        <v>1822690000</v>
       </c>
       <c r="E54" s="3">
-        <v>1711160000</v>
+        <v>1736930000</v>
       </c>
       <c r="F54" s="3">
-        <v>1610760000</v>
+        <v>1635020000</v>
       </c>
       <c r="G54" s="3">
-        <v>1459890000</v>
+        <v>1481880000</v>
       </c>
       <c r="H54" s="3">
-        <v>1352300000</v>
+        <v>1372660000</v>
       </c>
       <c r="I54" s="3">
-        <v>1321690000</v>
+        <v>1341590000</v>
       </c>
       <c r="J54" s="3">
-        <v>1313340000</v>
+        <v>1333120000</v>
       </c>
       <c r="K54" s="3">
         <v>1371410000</v>
@@ -2573,16 +2573,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>182769000</v>
+        <v>185521000</v>
       </c>
       <c r="E58" s="3">
-        <v>186236000</v>
+        <v>189041000</v>
       </c>
       <c r="F58" s="3">
-        <v>168819000</v>
+        <v>171361000</v>
       </c>
       <c r="G58" s="3">
-        <v>162231000</v>
+        <v>164674000</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>5</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>661100</v>
+        <v>671000</v>
       </c>
       <c r="E59" s="3">
-        <v>623900</v>
+        <v>633300</v>
       </c>
       <c r="F59" s="3">
-        <v>623700</v>
+        <v>633100</v>
       </c>
       <c r="G59" s="3">
-        <v>512800</v>
+        <v>520500</v>
       </c>
       <c r="H59" s="3">
-        <v>487700</v>
+        <v>495000</v>
       </c>
       <c r="I59" s="3">
-        <v>583700</v>
+        <v>592500</v>
       </c>
       <c r="J59" s="3">
-        <v>534000</v>
+        <v>542000</v>
       </c>
       <c r="K59" s="3">
         <v>521300</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>159757000</v>
+        <v>162163000</v>
       </c>
       <c r="E61" s="3">
-        <v>190616000</v>
+        <v>193486000</v>
       </c>
       <c r="F61" s="3">
-        <v>177578000</v>
+        <v>180252000</v>
       </c>
       <c r="G61" s="3">
-        <v>162470000</v>
+        <v>164916000</v>
       </c>
       <c r="H61" s="3">
-        <v>132032000</v>
+        <v>134020000</v>
       </c>
       <c r="I61" s="3">
-        <v>132049000</v>
+        <v>134038000</v>
       </c>
       <c r="J61" s="3">
-        <v>125602000</v>
+        <v>127494000</v>
       </c>
       <c r="K61" s="3">
         <v>115272000</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3331100</v>
+        <v>3381300</v>
       </c>
       <c r="E62" s="3">
-        <v>3429300</v>
+        <v>3481000</v>
       </c>
       <c r="F62" s="3">
-        <v>5162700</v>
+        <v>5240400</v>
       </c>
       <c r="G62" s="3">
-        <v>3332200</v>
+        <v>3382400</v>
       </c>
       <c r="H62" s="3">
-        <v>4143300</v>
+        <v>4205700</v>
       </c>
       <c r="I62" s="3">
-        <v>4747300</v>
+        <v>4818800</v>
       </c>
       <c r="J62" s="3">
-        <v>4147900</v>
+        <v>4210400</v>
       </c>
       <c r="K62" s="3">
         <v>5131000</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1711440000</v>
+        <v>1737210000</v>
       </c>
       <c r="E66" s="3">
-        <v>1630820000</v>
+        <v>1655380000</v>
       </c>
       <c r="F66" s="3">
-        <v>1532220000</v>
+        <v>1555300000</v>
       </c>
       <c r="G66" s="3">
-        <v>1388700000</v>
+        <v>1409610000</v>
       </c>
       <c r="H66" s="3">
-        <v>1280760000</v>
+        <v>1300050000</v>
       </c>
       <c r="I66" s="3">
-        <v>1252670000</v>
+        <v>1271540000</v>
       </c>
       <c r="J66" s="3">
-        <v>1248700000</v>
+        <v>1267500000</v>
       </c>
       <c r="K66" s="3">
         <v>1305870000</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>49300300</v>
+        <v>50042800</v>
       </c>
       <c r="E72" s="3">
-        <v>45935100</v>
+        <v>46626900</v>
       </c>
       <c r="F72" s="3">
-        <v>43122700</v>
+        <v>43772100</v>
       </c>
       <c r="G72" s="3">
-        <v>42086800</v>
+        <v>42720600</v>
       </c>
       <c r="H72" s="3">
-        <v>39820100</v>
+        <v>40419800</v>
       </c>
       <c r="I72" s="3">
-        <v>36887800</v>
+        <v>37443400</v>
       </c>
       <c r="J72" s="3">
-        <v>33467200</v>
+        <v>33971200</v>
       </c>
       <c r="K72" s="3">
         <v>33349600</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>84205900</v>
+        <v>85474100</v>
       </c>
       <c r="E76" s="3">
-        <v>80341900</v>
+        <v>81551900</v>
       </c>
       <c r="F76" s="3">
-        <v>78539300</v>
+        <v>79722100</v>
       </c>
       <c r="G76" s="3">
-        <v>71194300</v>
+        <v>72266500</v>
       </c>
       <c r="H76" s="3">
-        <v>71533200</v>
+        <v>72610500</v>
       </c>
       <c r="I76" s="3">
-        <v>69011400</v>
+        <v>70050800</v>
       </c>
       <c r="J76" s="3">
-        <v>64640500</v>
+        <v>65614000</v>
       </c>
       <c r="K76" s="3">
         <v>65537400</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>5350800</v>
+        <v>5431400</v>
       </c>
       <c r="E81" s="3">
-        <v>4692000</v>
+        <v>4762700</v>
       </c>
       <c r="F81" s="3">
-        <v>3405100</v>
+        <v>3456400</v>
       </c>
       <c r="G81" s="3">
-        <v>4673800</v>
+        <v>4744200</v>
       </c>
       <c r="H81" s="3">
-        <v>4825200</v>
+        <v>4897800</v>
       </c>
       <c r="I81" s="3">
-        <v>4876200</v>
+        <v>4949600</v>
       </c>
       <c r="J81" s="3">
-        <v>4691300</v>
+        <v>4761900</v>
       </c>
       <c r="K81" s="3">
         <v>4753100</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1779000</v>
+        <v>1805800</v>
       </c>
       <c r="E83" s="3">
-        <v>1606300</v>
+        <v>1630500</v>
       </c>
       <c r="F83" s="3">
-        <v>1508500</v>
+        <v>1531200</v>
       </c>
       <c r="G83" s="3">
-        <v>1505500</v>
+        <v>1528200</v>
       </c>
       <c r="H83" s="3">
-        <v>1958300</v>
+        <v>1987800</v>
       </c>
       <c r="I83" s="3">
-        <v>2036900</v>
+        <v>2067600</v>
       </c>
       <c r="J83" s="3">
-        <v>2020300</v>
+        <v>2050700</v>
       </c>
       <c r="K83" s="3">
         <v>1955200</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-39144000</v>
+        <v>-39733600</v>
       </c>
       <c r="E89" s="3">
-        <v>10261600</v>
+        <v>10416200</v>
       </c>
       <c r="F89" s="3">
-        <v>124805100</v>
+        <v>126684700</v>
       </c>
       <c r="G89" s="3">
-        <v>47061300</v>
+        <v>47770000</v>
       </c>
       <c r="H89" s="3">
-        <v>30529100</v>
+        <v>30988900</v>
       </c>
       <c r="I89" s="3">
-        <v>62046600</v>
+        <v>62981000</v>
       </c>
       <c r="J89" s="3">
-        <v>29995000</v>
+        <v>30446700</v>
       </c>
       <c r="K89" s="3">
         <v>-8285300</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-664100</v>
+        <v>-674100</v>
       </c>
       <c r="E91" s="3">
-        <v>-614800</v>
+        <v>-624100</v>
       </c>
       <c r="F91" s="3">
-        <v>-969100</v>
+        <v>-983700</v>
       </c>
       <c r="G91" s="3">
-        <v>-684300</v>
+        <v>-694600</v>
       </c>
       <c r="H91" s="3">
-        <v>-3387800</v>
+        <v>-3438800</v>
       </c>
       <c r="I91" s="3">
-        <v>-4731400</v>
+        <v>-4802700</v>
       </c>
       <c r="J91" s="3">
-        <v>-3292300</v>
+        <v>-3341800</v>
       </c>
       <c r="K91" s="3">
         <v>-3890100</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>39382200</v>
+        <v>39975300</v>
       </c>
       <c r="E94" s="3">
-        <v>-15981200</v>
+        <v>-16221900</v>
       </c>
       <c r="F94" s="3">
-        <v>-50994400</v>
+        <v>-51762400</v>
       </c>
       <c r="G94" s="3">
-        <v>-19997400</v>
+        <v>-20298600</v>
       </c>
       <c r="H94" s="3">
-        <v>6681600</v>
+        <v>6782200</v>
       </c>
       <c r="I94" s="3">
-        <v>-22544800</v>
+        <v>-22884300</v>
       </c>
       <c r="J94" s="3">
-        <v>3860100</v>
+        <v>3918300</v>
       </c>
       <c r="K94" s="3">
         <v>38521000</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2002600</v>
+        <v>-2032800</v>
       </c>
       <c r="E96" s="3">
-        <v>-1819700</v>
+        <v>-1847200</v>
       </c>
       <c r="F96" s="3">
-        <v>-1773700</v>
+        <v>-1800400</v>
       </c>
       <c r="G96" s="3">
-        <v>-1698300</v>
+        <v>-1723900</v>
       </c>
       <c r="H96" s="3">
-        <v>-1630700</v>
+        <v>-1655300</v>
       </c>
       <c r="I96" s="3">
-        <v>-1451300</v>
+        <v>-1473200</v>
       </c>
       <c r="J96" s="3">
-        <v>-1361700</v>
+        <v>-1382200</v>
       </c>
       <c r="K96" s="3">
         <v>-1557800</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2375600</v>
+        <v>-2411400</v>
       </c>
       <c r="E100" s="3">
-        <v>-3222600</v>
+        <v>-3271200</v>
       </c>
       <c r="F100" s="3">
-        <v>-3735500</v>
+        <v>-3791800</v>
       </c>
       <c r="G100" s="3">
-        <v>-6803000</v>
+        <v>-6905500</v>
       </c>
       <c r="H100" s="3">
-        <v>-4201900</v>
+        <v>-4265200</v>
       </c>
       <c r="I100" s="3">
-        <v>-2327100</v>
+        <v>-2362200</v>
       </c>
       <c r="J100" s="3">
-        <v>-1105700</v>
+        <v>-1122400</v>
       </c>
       <c r="K100" s="3">
         <v>-411600</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2351100</v>
+        <v>2386500</v>
       </c>
       <c r="E101" s="3">
-        <v>2440800</v>
+        <v>2477500</v>
       </c>
       <c r="F101" s="3">
-        <v>1061800</v>
+        <v>1077800</v>
       </c>
       <c r="G101" s="3">
-        <v>-494500</v>
+        <v>-502000</v>
       </c>
       <c r="H101" s="3">
-        <v>1106500</v>
+        <v>1123200</v>
       </c>
       <c r="I101" s="3">
-        <v>-623300</v>
+        <v>-632700</v>
       </c>
       <c r="J101" s="3">
-        <v>-70100</v>
+        <v>-71100</v>
       </c>
       <c r="K101" s="3">
         <v>-731900</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>213600</v>
+        <v>216900</v>
       </c>
       <c r="E102" s="3">
-        <v>-6501500</v>
+        <v>-6599400</v>
       </c>
       <c r="F102" s="3">
-        <v>71137000</v>
+        <v>72208300</v>
       </c>
       <c r="G102" s="3">
-        <v>19766300</v>
+        <v>20063900</v>
       </c>
       <c r="H102" s="3">
-        <v>34115300</v>
+        <v>34629100</v>
       </c>
       <c r="I102" s="3">
-        <v>36551300</v>
+        <v>37101800</v>
       </c>
       <c r="J102" s="3">
-        <v>32679300</v>
+        <v>33171500</v>
       </c>
       <c r="K102" s="3">
         <v>29092200</v>

--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -656,111 +656,117 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>25475300</v>
+        <v>39642300</v>
       </c>
       <c r="E8" s="3">
-        <v>12859900</v>
+        <v>24114600</v>
       </c>
       <c r="F8" s="3">
-        <v>12489500</v>
+        <v>12173000</v>
       </c>
       <c r="G8" s="3">
-        <v>16555900</v>
+        <v>11822400</v>
       </c>
       <c r="H8" s="3">
-        <v>16775200</v>
+        <v>15671600</v>
       </c>
       <c r="I8" s="3">
-        <v>14597400</v>
+        <v>15879200</v>
       </c>
       <c r="J8" s="3">
+        <v>13817700</v>
+      </c>
+      <c r="K8" s="3">
         <v>12887100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>13732100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>16138200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16534000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>15686800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15461400</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -800,9 +806,12 @@
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -842,9 +851,12 @@
       <c r="O10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,9 +960,12 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -986,26 +1005,29 @@
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>-1317900</v>
+      <c r="D15" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E15" s="3">
-        <v>-1310800</v>
+        <v>-1247500</v>
       </c>
       <c r="F15" s="3">
-        <v>-1228300</v>
+        <v>-1240800</v>
       </c>
       <c r="G15" s="3">
-        <v>-1218400</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>5</v>
+        <v>-1162700</v>
+      </c>
+      <c r="H15" s="3">
+        <v>-1153300</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>5</v>
@@ -1022,15 +1044,18 @@
       <c r="M15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N15" s="3">
+      <c r="N15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="O15" s="3">
         <v>-1185200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>-1099400</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>15060100</v>
+        <v>28291000</v>
       </c>
       <c r="E17" s="3">
-        <v>4219500</v>
+        <v>14255700</v>
       </c>
       <c r="F17" s="3">
-        <v>5771200</v>
+        <v>3994100</v>
       </c>
       <c r="G17" s="3">
-        <v>9053400</v>
+        <v>5463000</v>
       </c>
       <c r="H17" s="3">
-        <v>8398900</v>
+        <v>8569800</v>
       </c>
       <c r="I17" s="3">
-        <v>5789600</v>
+        <v>7950300</v>
       </c>
       <c r="J17" s="3">
+        <v>5480400</v>
+      </c>
+      <c r="K17" s="3">
         <v>4738300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3929800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3297800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2380800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2923100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2835200</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>10415200</v>
+        <v>11351300</v>
       </c>
       <c r="E18" s="3">
-        <v>8640400</v>
+        <v>9858900</v>
       </c>
       <c r="F18" s="3">
-        <v>6718300</v>
+        <v>8178900</v>
       </c>
       <c r="G18" s="3">
-        <v>7502500</v>
+        <v>6359500</v>
       </c>
       <c r="H18" s="3">
-        <v>8376300</v>
+        <v>7101800</v>
       </c>
       <c r="I18" s="3">
-        <v>8807800</v>
+        <v>7928900</v>
       </c>
       <c r="J18" s="3">
+        <v>8337400</v>
+      </c>
+      <c r="K18" s="3">
         <v>8148800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>9802300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>12840400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14153200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12763800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12626200</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,92 +1178,99 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3011500</v>
+        <v>-2787100</v>
       </c>
       <c r="E20" s="3">
-        <v>-2375000</v>
+        <v>-2850700</v>
       </c>
       <c r="F20" s="3">
-        <v>-2187400</v>
+        <v>-2248100</v>
       </c>
       <c r="G20" s="3">
-        <v>-1513000</v>
+        <v>-2070600</v>
       </c>
       <c r="H20" s="3">
-        <v>-803400</v>
+        <v>-1432200</v>
       </c>
       <c r="I20" s="3">
-        <v>-1334200</v>
+        <v>-760500</v>
       </c>
       <c r="J20" s="3">
+        <v>-1262900</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1548300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2598000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1671400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1121300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4503500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4386900</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>9217600</v>
+        <v>10431000</v>
       </c>
       <c r="E21" s="3">
-        <v>7903200</v>
+        <v>8715000</v>
       </c>
       <c r="F21" s="3">
-        <v>6068900</v>
+        <v>7471800</v>
       </c>
       <c r="G21" s="3">
-        <v>7524400</v>
+        <v>5736000</v>
       </c>
       <c r="H21" s="3">
-        <v>9569600</v>
+        <v>7113800</v>
       </c>
       <c r="I21" s="3">
-        <v>9550400</v>
+        <v>9047100</v>
       </c>
       <c r="J21" s="3">
+        <v>9028500</v>
+      </c>
+      <c r="K21" s="3">
         <v>8660400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9140900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>13315400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>15152100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>10302300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>9804500</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1271,93 +1310,102 @@
       <c r="O22" s="3">
         <v>0</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>7403700</v>
+        <v>8564200</v>
       </c>
       <c r="E23" s="3">
-        <v>6265400</v>
+        <v>7008300</v>
       </c>
       <c r="F23" s="3">
-        <v>4530900</v>
+        <v>5930800</v>
       </c>
       <c r="G23" s="3">
-        <v>5989500</v>
+        <v>4288900</v>
       </c>
       <c r="H23" s="3">
-        <v>7572900</v>
+        <v>5669600</v>
       </c>
       <c r="I23" s="3">
-        <v>7473600</v>
+        <v>7168400</v>
       </c>
       <c r="J23" s="3">
+        <v>7074500</v>
+      </c>
+      <c r="K23" s="3">
         <v>6600500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>7204200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>11169000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>13031900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>8260200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8239300</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>1901700</v>
+        <v>2384000</v>
       </c>
       <c r="E24" s="3">
-        <v>1446000</v>
+        <v>1800100</v>
       </c>
       <c r="F24" s="3">
-        <v>1053800</v>
+        <v>1368700</v>
       </c>
       <c r="G24" s="3">
-        <v>1130200</v>
+        <v>997500</v>
       </c>
       <c r="H24" s="3">
-        <v>2233800</v>
+        <v>1069800</v>
       </c>
       <c r="I24" s="3">
-        <v>1823300</v>
+        <v>2114500</v>
       </c>
       <c r="J24" s="3">
+        <v>1725900</v>
+      </c>
+      <c r="K24" s="3">
         <v>1152200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1654100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3764800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4202700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2319400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4162400</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>5502000</v>
+        <v>6180200</v>
       </c>
       <c r="E26" s="3">
-        <v>4819500</v>
+        <v>5208100</v>
       </c>
       <c r="F26" s="3">
-        <v>3477100</v>
+        <v>4562000</v>
       </c>
       <c r="G26" s="3">
-        <v>4859300</v>
+        <v>3291400</v>
       </c>
       <c r="H26" s="3">
-        <v>5339100</v>
+        <v>4599700</v>
       </c>
       <c r="I26" s="3">
-        <v>5650300</v>
+        <v>5053900</v>
       </c>
       <c r="J26" s="3">
+        <v>5348500</v>
+      </c>
+      <c r="K26" s="3">
         <v>5448300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5550200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7404200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>8829200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>5940900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>4076900</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>5431400</v>
+        <v>6143600</v>
       </c>
       <c r="E27" s="3">
-        <v>4762700</v>
+        <v>5141300</v>
       </c>
       <c r="F27" s="3">
-        <v>3456400</v>
+        <v>4508300</v>
       </c>
       <c r="G27" s="3">
-        <v>4744200</v>
+        <v>3271700</v>
       </c>
       <c r="H27" s="3">
-        <v>4897800</v>
+        <v>4490800</v>
       </c>
       <c r="I27" s="3">
-        <v>4949600</v>
+        <v>4636200</v>
       </c>
       <c r="J27" s="3">
+        <v>4685300</v>
+      </c>
+      <c r="K27" s="3">
         <v>4761900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4753100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>6428300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>7651900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>3743300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3058400</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1565,9 +1625,12 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3011500</v>
+        <v>2787100</v>
       </c>
       <c r="E32" s="3">
-        <v>2375000</v>
+        <v>2850700</v>
       </c>
       <c r="F32" s="3">
-        <v>2187400</v>
+        <v>2248100</v>
       </c>
       <c r="G32" s="3">
-        <v>1513000</v>
+        <v>2070600</v>
       </c>
       <c r="H32" s="3">
-        <v>803400</v>
+        <v>1432200</v>
       </c>
       <c r="I32" s="3">
-        <v>1334200</v>
+        <v>760500</v>
       </c>
       <c r="J32" s="3">
+        <v>1262900</v>
+      </c>
+      <c r="K32" s="3">
         <v>1548300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2598000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1671400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1121300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4503500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4386900</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5431400</v>
+        <v>6143600</v>
       </c>
       <c r="E33" s="3">
-        <v>4762700</v>
+        <v>5141300</v>
       </c>
       <c r="F33" s="3">
-        <v>3456400</v>
+        <v>4508300</v>
       </c>
       <c r="G33" s="3">
-        <v>4744200</v>
+        <v>3271700</v>
       </c>
       <c r="H33" s="3">
-        <v>4897800</v>
+        <v>4490800</v>
       </c>
       <c r="I33" s="3">
-        <v>4949600</v>
+        <v>4636200</v>
       </c>
       <c r="J33" s="3">
+        <v>4685300</v>
+      </c>
+      <c r="K33" s="3">
         <v>4761900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4753100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>6428300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>7651900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>3743300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3058400</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>5431400</v>
+        <v>6143600</v>
       </c>
       <c r="E35" s="3">
-        <v>4762700</v>
+        <v>5141300</v>
       </c>
       <c r="F35" s="3">
-        <v>3456400</v>
+        <v>4508300</v>
       </c>
       <c r="G35" s="3">
-        <v>4744200</v>
+        <v>3271700</v>
       </c>
       <c r="H35" s="3">
-        <v>4897800</v>
+        <v>4490800</v>
       </c>
       <c r="I35" s="3">
-        <v>4949600</v>
+        <v>4636200</v>
       </c>
       <c r="J35" s="3">
+        <v>4685300</v>
+      </c>
+      <c r="K35" s="3">
         <v>4761900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4753100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>6428300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>7651900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>3743300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3058400</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,92 +1986,99 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>511660000</v>
+        <v>498553000</v>
       </c>
       <c r="E41" s="3">
-        <v>504099000</v>
+        <v>484331000</v>
       </c>
       <c r="F41" s="3">
-        <v>489114000</v>
+        <v>477174000</v>
       </c>
       <c r="G41" s="3">
-        <v>416320000</v>
+        <v>462989000</v>
       </c>
       <c r="H41" s="3">
-        <v>386952000</v>
+        <v>394084000</v>
       </c>
       <c r="I41" s="3">
-        <v>362158000</v>
+        <v>366284000</v>
       </c>
       <c r="J41" s="3">
+        <v>342814000</v>
+      </c>
+      <c r="K41" s="3">
         <v>315874000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>314501000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>339059000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>302199000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>217778000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>84465200</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>224440000</v>
+        <v>257568000</v>
       </c>
       <c r="E42" s="3">
-        <v>196704000</v>
+        <v>212452000</v>
       </c>
       <c r="F42" s="3">
-        <v>184633000</v>
+        <v>186198000</v>
       </c>
       <c r="G42" s="3">
-        <v>193031000</v>
+        <v>174772000</v>
       </c>
       <c r="H42" s="3">
-        <v>166042000</v>
+        <v>182721000</v>
       </c>
       <c r="I42" s="3">
-        <v>158592000</v>
+        <v>157174000</v>
       </c>
       <c r="J42" s="3">
+        <v>150122000</v>
+      </c>
+      <c r="K42" s="3">
         <v>164672000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>174560000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>189608000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>163523000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>183032000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>39736300</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2026,9 +2118,12 @@
       <c r="O43" s="3">
         <v>0</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2068,9 +2163,12 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2110,9 +2208,12 @@
       <c r="O45" s="3">
         <v>0</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2152,135 +2253,147 @@
       <c r="O46" s="3">
         <v>0</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>9089800</v>
+      <c r="D47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E47" s="3">
-        <v>8000200</v>
+        <v>8604300</v>
       </c>
       <c r="F47" s="3">
-        <v>6481700</v>
+        <v>7572900</v>
       </c>
       <c r="G47" s="3">
-        <v>6366900</v>
+        <v>6135500</v>
       </c>
       <c r="H47" s="3">
-        <v>6577200</v>
+        <v>6026800</v>
       </c>
       <c r="I47" s="3">
-        <v>4604400</v>
+        <v>6225900</v>
       </c>
       <c r="J47" s="3">
+        <v>4358500</v>
+      </c>
+      <c r="K47" s="3">
         <v>4074700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4486600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4979100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3411000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4711900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1868200</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>10073100</v>
+        <v>6423900</v>
       </c>
       <c r="E48" s="3">
-        <v>9821900</v>
+        <v>9535100</v>
       </c>
       <c r="F48" s="3">
-        <v>9833600</v>
+        <v>9297300</v>
       </c>
       <c r="G48" s="3">
-        <v>9775200</v>
+        <v>9308400</v>
       </c>
       <c r="H48" s="3">
-        <v>10141700</v>
+        <v>9253100</v>
       </c>
       <c r="I48" s="3">
-        <v>23422400</v>
+        <v>9600000</v>
       </c>
       <c r="J48" s="3">
+        <v>22171300</v>
+      </c>
+      <c r="K48" s="3">
         <v>20905100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>21457800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>23635400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>21496600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>36213000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>20247600</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6051500</v>
+        <v>6231400</v>
       </c>
       <c r="E49" s="3">
-        <v>6058000</v>
+        <v>5728300</v>
       </c>
       <c r="F49" s="3">
-        <v>4979200</v>
+        <v>5734500</v>
       </c>
       <c r="G49" s="3">
-        <v>5079100</v>
+        <v>4713300</v>
       </c>
       <c r="H49" s="3">
-        <v>5184600</v>
+        <v>4807800</v>
       </c>
       <c r="I49" s="3">
-        <v>5834000</v>
+        <v>4907700</v>
       </c>
       <c r="J49" s="3">
+        <v>5522400</v>
+      </c>
+      <c r="K49" s="3">
         <v>6379500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6455200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6990800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>7510200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>15399600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16256900</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>5248700</v>
+        <v>6285700</v>
       </c>
       <c r="E52" s="3">
-        <v>4649000</v>
+        <v>4968300</v>
       </c>
       <c r="F52" s="3">
-        <v>4012800</v>
+        <v>4400700</v>
       </c>
       <c r="G52" s="3">
-        <v>1731400</v>
+        <v>3798500</v>
       </c>
       <c r="H52" s="3">
-        <v>2491600</v>
+        <v>1638900</v>
       </c>
       <c r="I52" s="3">
-        <v>2770300</v>
+        <v>2358600</v>
       </c>
       <c r="J52" s="3">
+        <v>2622400</v>
+      </c>
+      <c r="K52" s="3">
         <v>2547200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2418900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4299900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2684900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7796700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8355100</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1822690000</v>
+        <v>1883610000</v>
       </c>
       <c r="E54" s="3">
-        <v>1736930000</v>
+        <v>1725330000</v>
       </c>
       <c r="F54" s="3">
-        <v>1635020000</v>
+        <v>1644160000</v>
       </c>
       <c r="G54" s="3">
-        <v>1481880000</v>
+        <v>1547690000</v>
       </c>
       <c r="H54" s="3">
-        <v>1372660000</v>
+        <v>1402730000</v>
       </c>
       <c r="I54" s="3">
-        <v>1341590000</v>
+        <v>1299350000</v>
       </c>
       <c r="J54" s="3">
+        <v>1269930000</v>
+      </c>
+      <c r="K54" s="3">
         <v>1333120000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1371410000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1564770000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1479660000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1343090000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1281880000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,8 +2654,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2566,26 +2696,29 @@
       <c r="O57" s="3">
         <v>0</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>185521000</v>
+      <c r="D58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E58" s="3">
-        <v>189041000</v>
+        <v>175612000</v>
       </c>
       <c r="F58" s="3">
-        <v>171361000</v>
+        <v>178944000</v>
       </c>
       <c r="G58" s="3">
-        <v>164674000</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>5</v>
+        <v>162208000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>155878000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>5</v>
@@ -2593,8 +2726,8 @@
       <c r="J58" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
+      <c r="K58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L58" s="3">
         <v>0</v>
@@ -2608,51 +2741,57 @@
       <c r="O58" s="3">
         <v>0</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>671000</v>
+        <v>765000</v>
       </c>
       <c r="E59" s="3">
-        <v>633300</v>
+        <v>635200</v>
       </c>
       <c r="F59" s="3">
-        <v>633100</v>
+        <v>599500</v>
       </c>
       <c r="G59" s="3">
-        <v>520500</v>
+        <v>599300</v>
       </c>
       <c r="H59" s="3">
-        <v>495000</v>
+        <v>492700</v>
       </c>
       <c r="I59" s="3">
-        <v>592500</v>
+        <v>468600</v>
       </c>
       <c r="J59" s="3">
+        <v>560800</v>
+      </c>
+      <c r="K59" s="3">
         <v>542000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>521300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>654300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>681000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>4547000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>2359800</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2692,93 +2831,102 @@
       <c r="O60" s="3">
         <v>0</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>162163000</v>
+        <v>177527000</v>
       </c>
       <c r="E61" s="3">
-        <v>193486000</v>
+        <v>153501000</v>
       </c>
       <c r="F61" s="3">
-        <v>180252000</v>
+        <v>183152000</v>
       </c>
       <c r="G61" s="3">
-        <v>164916000</v>
+        <v>170625000</v>
       </c>
       <c r="H61" s="3">
-        <v>134020000</v>
+        <v>156108000</v>
       </c>
       <c r="I61" s="3">
-        <v>134038000</v>
+        <v>126862000</v>
       </c>
       <c r="J61" s="3">
+        <v>126879000</v>
+      </c>
+      <c r="K61" s="3">
         <v>127494000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>115272000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>137357000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>110944000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>58862700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>94132200</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>3381300</v>
+        <v>5970500</v>
       </c>
       <c r="E62" s="3">
-        <v>3481000</v>
+        <v>3200700</v>
       </c>
       <c r="F62" s="3">
-        <v>5240400</v>
+        <v>3295100</v>
       </c>
       <c r="G62" s="3">
-        <v>3382400</v>
+        <v>4960500</v>
       </c>
       <c r="H62" s="3">
-        <v>4205700</v>
+        <v>3201700</v>
       </c>
       <c r="I62" s="3">
-        <v>4818800</v>
+        <v>3981100</v>
       </c>
       <c r="J62" s="3">
+        <v>4561400</v>
+      </c>
+      <c r="K62" s="3">
         <v>4210400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5131000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>7540600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3803400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6030000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1152100</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1737210000</v>
+        <v>1790070000</v>
       </c>
       <c r="E66" s="3">
-        <v>1655380000</v>
+        <v>1644430000</v>
       </c>
       <c r="F66" s="3">
-        <v>1555300000</v>
+        <v>1566960000</v>
       </c>
       <c r="G66" s="3">
-        <v>1409610000</v>
+        <v>1472220000</v>
       </c>
       <c r="H66" s="3">
-        <v>1300050000</v>
+        <v>1334320000</v>
       </c>
       <c r="I66" s="3">
-        <v>1271540000</v>
+        <v>1230610000</v>
       </c>
       <c r="J66" s="3">
+        <v>1203620000</v>
+      </c>
+      <c r="K66" s="3">
         <v>1267500000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1305870000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1487790000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1412960000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1284350000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1233310000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>50042800</v>
+        <v>50047300</v>
       </c>
       <c r="E72" s="3">
-        <v>46626900</v>
+        <v>47369900</v>
       </c>
       <c r="F72" s="3">
-        <v>43772100</v>
+        <v>44136500</v>
       </c>
       <c r="G72" s="3">
-        <v>42720600</v>
+        <v>41434100</v>
       </c>
       <c r="H72" s="3">
-        <v>40419800</v>
+        <v>40438800</v>
       </c>
       <c r="I72" s="3">
-        <v>37443400</v>
+        <v>38260800</v>
       </c>
       <c r="J72" s="3">
+        <v>35443400</v>
+      </c>
+      <c r="K72" s="3">
         <v>33971200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33349600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>34979000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>31894000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>57285400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>21765900</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>85474100</v>
+        <v>93537400</v>
       </c>
       <c r="E76" s="3">
-        <v>81551900</v>
+        <v>80908700</v>
       </c>
       <c r="F76" s="3">
-        <v>79722100</v>
+        <v>77196000</v>
       </c>
       <c r="G76" s="3">
-        <v>72266500</v>
+        <v>75464000</v>
       </c>
       <c r="H76" s="3">
-        <v>72610500</v>
+        <v>68406600</v>
       </c>
       <c r="I76" s="3">
-        <v>70050800</v>
+        <v>68732200</v>
       </c>
       <c r="J76" s="3">
+        <v>66309200</v>
+      </c>
+      <c r="K76" s="3">
         <v>65614000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>65537400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>76979300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>66693800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58740700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>48567700</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>5431400</v>
+        <v>6143600</v>
       </c>
       <c r="E81" s="3">
-        <v>4762700</v>
+        <v>5141300</v>
       </c>
       <c r="F81" s="3">
-        <v>3456400</v>
+        <v>4508300</v>
       </c>
       <c r="G81" s="3">
-        <v>4744200</v>
+        <v>3271700</v>
       </c>
       <c r="H81" s="3">
-        <v>4897800</v>
+        <v>4490800</v>
       </c>
       <c r="I81" s="3">
-        <v>4949600</v>
+        <v>4636200</v>
       </c>
       <c r="J81" s="3">
+        <v>4685300</v>
+      </c>
+      <c r="K81" s="3">
         <v>4761900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4753100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>6428300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>7651900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>3743300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3058400</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1805800</v>
+        <v>1869800</v>
       </c>
       <c r="E83" s="3">
-        <v>1630500</v>
+        <v>1709400</v>
       </c>
       <c r="F83" s="3">
-        <v>1531200</v>
+        <v>1543400</v>
       </c>
       <c r="G83" s="3">
-        <v>1528200</v>
+        <v>1449400</v>
       </c>
       <c r="H83" s="3">
-        <v>1987800</v>
+        <v>1446500</v>
       </c>
       <c r="I83" s="3">
-        <v>2067600</v>
+        <v>1881600</v>
       </c>
       <c r="J83" s="3">
+        <v>1957100</v>
+      </c>
+      <c r="K83" s="3">
         <v>2050700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1955200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>2121500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2111000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2037600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1563500</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-39733600</v>
+        <v>4101500</v>
       </c>
       <c r="E89" s="3">
-        <v>10416200</v>
+        <v>-37611300</v>
       </c>
       <c r="F89" s="3">
-        <v>126684700</v>
+        <v>9859800</v>
       </c>
       <c r="G89" s="3">
-        <v>47770000</v>
+        <v>119918200</v>
       </c>
       <c r="H89" s="3">
-        <v>30988900</v>
+        <v>45218500</v>
       </c>
       <c r="I89" s="3">
-        <v>62981000</v>
+        <v>29333700</v>
       </c>
       <c r="J89" s="3">
+        <v>59617000</v>
+      </c>
+      <c r="K89" s="3">
         <v>30446700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-8285300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>69840100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>76062400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>21574500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>11941900</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-674100</v>
+        <v>-904000</v>
       </c>
       <c r="E91" s="3">
-        <v>-624100</v>
+        <v>-638100</v>
       </c>
       <c r="F91" s="3">
-        <v>-983700</v>
+        <v>-590700</v>
       </c>
       <c r="G91" s="3">
-        <v>-694600</v>
+        <v>-931100</v>
       </c>
       <c r="H91" s="3">
-        <v>-3438800</v>
+        <v>-657500</v>
       </c>
       <c r="I91" s="3">
-        <v>-4802700</v>
+        <v>-3255200</v>
       </c>
       <c r="J91" s="3">
+        <v>-4546200</v>
+      </c>
+      <c r="K91" s="3">
         <v>-3341800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3890100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4938600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4260700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5273500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1175100</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>39975300</v>
+        <v>-5862600</v>
       </c>
       <c r="E94" s="3">
-        <v>-16221900</v>
+        <v>37840200</v>
       </c>
       <c r="F94" s="3">
-        <v>-51762400</v>
+        <v>-15355400</v>
       </c>
       <c r="G94" s="3">
-        <v>-20298600</v>
+        <v>-48997600</v>
       </c>
       <c r="H94" s="3">
-        <v>6782200</v>
+        <v>-19214400</v>
       </c>
       <c r="I94" s="3">
-        <v>-22884300</v>
+        <v>6419900</v>
       </c>
       <c r="J94" s="3">
+        <v>-21662000</v>
+      </c>
+      <c r="K94" s="3">
         <v>3918300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>38521000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12429800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>133008000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>12797800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-22347400</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2032800</v>
+        <v>-2220300</v>
       </c>
       <c r="E96" s="3">
-        <v>-1847200</v>
+        <v>-1924200</v>
       </c>
       <c r="F96" s="3">
-        <v>-1800400</v>
+        <v>-1748500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1723900</v>
+        <v>-1704200</v>
       </c>
       <c r="H96" s="3">
-        <v>-1655300</v>
+        <v>-1631800</v>
       </c>
       <c r="I96" s="3">
-        <v>-1473200</v>
+        <v>-1566900</v>
       </c>
       <c r="J96" s="3">
+        <v>-1394500</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1382200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1557800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1457900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1557000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2458000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1283000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-2411400</v>
+        <v>1790800</v>
       </c>
       <c r="E100" s="3">
-        <v>-3271200</v>
+        <v>-2282600</v>
       </c>
       <c r="F100" s="3">
-        <v>-3791800</v>
+        <v>-3096500</v>
       </c>
       <c r="G100" s="3">
-        <v>-6905500</v>
+        <v>-3589300</v>
       </c>
       <c r="H100" s="3">
-        <v>-4265200</v>
+        <v>-6536700</v>
       </c>
       <c r="I100" s="3">
-        <v>-2362200</v>
+        <v>-4037400</v>
       </c>
       <c r="J100" s="3">
+        <v>-2236000</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1122400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-411600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2581100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-9515500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6725300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2759000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2386500</v>
+        <v>3262900</v>
       </c>
       <c r="E101" s="3">
-        <v>2477500</v>
+        <v>2259000</v>
       </c>
       <c r="F101" s="3">
-        <v>1077800</v>
+        <v>2345200</v>
       </c>
       <c r="G101" s="3">
-        <v>-502000</v>
+        <v>1020200</v>
       </c>
       <c r="H101" s="3">
-        <v>1123200</v>
+        <v>-475200</v>
       </c>
       <c r="I101" s="3">
-        <v>-632700</v>
+        <v>1063200</v>
       </c>
       <c r="J101" s="3">
+        <v>-598900</v>
+      </c>
+      <c r="K101" s="3">
         <v>-71100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-731900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1515800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>51100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>5676200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-557600</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>216900</v>
+        <v>3292600</v>
       </c>
       <c r="E102" s="3">
-        <v>-6599400</v>
+        <v>205300</v>
       </c>
       <c r="F102" s="3">
-        <v>72208300</v>
+        <v>-6246900</v>
       </c>
       <c r="G102" s="3">
-        <v>20063900</v>
+        <v>68351500</v>
       </c>
       <c r="H102" s="3">
-        <v>34629100</v>
+        <v>18992300</v>
       </c>
       <c r="I102" s="3">
-        <v>37101800</v>
+        <v>32779500</v>
       </c>
       <c r="J102" s="3">
+        <v>35120100</v>
+      </c>
+      <c r="K102" s="3">
         <v>33171500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>29092200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>56345100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>199606000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33323200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13722100</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>39642300</v>
+        <v>44116000</v>
       </c>
       <c r="E8" s="3">
-        <v>24114600</v>
+        <v>26836000</v>
       </c>
       <c r="F8" s="3">
-        <v>12173000</v>
+        <v>13546800</v>
       </c>
       <c r="G8" s="3">
-        <v>11822400</v>
+        <v>13156600</v>
       </c>
       <c r="H8" s="3">
-        <v>15671600</v>
+        <v>17440200</v>
       </c>
       <c r="I8" s="3">
-        <v>15879200</v>
+        <v>17671200</v>
       </c>
       <c r="J8" s="3">
-        <v>13817700</v>
+        <v>15377100</v>
       </c>
       <c r="K8" s="3">
         <v>12887100</v>
@@ -1018,16 +1018,16 @@
         <v>5</v>
       </c>
       <c r="E15" s="3">
-        <v>-1247500</v>
+        <v>-1388300</v>
       </c>
       <c r="F15" s="3">
-        <v>-1240800</v>
+        <v>-1380800</v>
       </c>
       <c r="G15" s="3">
-        <v>-1162700</v>
+        <v>-1293900</v>
       </c>
       <c r="H15" s="3">
-        <v>-1153300</v>
+        <v>-1283400</v>
       </c>
       <c r="I15" s="3" t="s">
         <v>5</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>28291000</v>
+        <v>32504100</v>
       </c>
       <c r="E17" s="3">
-        <v>14255700</v>
+        <v>15864500</v>
       </c>
       <c r="F17" s="3">
-        <v>3994100</v>
+        <v>4444900</v>
       </c>
       <c r="G17" s="3">
-        <v>5463000</v>
+        <v>6079500</v>
       </c>
       <c r="H17" s="3">
-        <v>8569800</v>
+        <v>9537000</v>
       </c>
       <c r="I17" s="3">
-        <v>7950300</v>
+        <v>8847600</v>
       </c>
       <c r="J17" s="3">
-        <v>5480400</v>
+        <v>6098900</v>
       </c>
       <c r="K17" s="3">
         <v>4738300</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11351300</v>
+        <v>11611900</v>
       </c>
       <c r="E18" s="3">
-        <v>9858900</v>
+        <v>10971500</v>
       </c>
       <c r="F18" s="3">
-        <v>8178900</v>
+        <v>9101900</v>
       </c>
       <c r="G18" s="3">
-        <v>6359500</v>
+        <v>7077100</v>
       </c>
       <c r="H18" s="3">
-        <v>7101800</v>
+        <v>7903200</v>
       </c>
       <c r="I18" s="3">
-        <v>7928900</v>
+        <v>8823700</v>
       </c>
       <c r="J18" s="3">
-        <v>8337400</v>
+        <v>9278300</v>
       </c>
       <c r="K18" s="3">
         <v>8148800</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2787100</v>
+        <v>-2081300</v>
       </c>
       <c r="E20" s="3">
-        <v>-2850700</v>
+        <v>-3172400</v>
       </c>
       <c r="F20" s="3">
-        <v>-2248100</v>
+        <v>-2501800</v>
       </c>
       <c r="G20" s="3">
-        <v>-2070600</v>
+        <v>-2304300</v>
       </c>
       <c r="H20" s="3">
-        <v>-1432200</v>
+        <v>-1593900</v>
       </c>
       <c r="I20" s="3">
-        <v>-760500</v>
+        <v>-846300</v>
       </c>
       <c r="J20" s="3">
-        <v>-1262900</v>
+        <v>-1405400</v>
       </c>
       <c r="K20" s="3">
         <v>-1548300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>10431000</v>
+        <v>11596800</v>
       </c>
       <c r="E21" s="3">
-        <v>8715000</v>
+        <v>9688000</v>
       </c>
       <c r="F21" s="3">
-        <v>7471800</v>
+        <v>8305600</v>
       </c>
       <c r="G21" s="3">
-        <v>5736000</v>
+        <v>6374500</v>
       </c>
       <c r="H21" s="3">
-        <v>7113800</v>
+        <v>7907800</v>
       </c>
       <c r="I21" s="3">
-        <v>9047100</v>
+        <v>10056700</v>
       </c>
       <c r="J21" s="3">
-        <v>9028500</v>
+        <v>10035500</v>
       </c>
       <c r="K21" s="3">
         <v>8660400</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>8564200</v>
+        <v>9530700</v>
       </c>
       <c r="E23" s="3">
-        <v>7008300</v>
+        <v>7799200</v>
       </c>
       <c r="F23" s="3">
-        <v>5930800</v>
+        <v>6600100</v>
       </c>
       <c r="G23" s="3">
-        <v>4288900</v>
+        <v>4772900</v>
       </c>
       <c r="H23" s="3">
-        <v>5669600</v>
+        <v>6309400</v>
       </c>
       <c r="I23" s="3">
-        <v>7168400</v>
+        <v>7977400</v>
       </c>
       <c r="J23" s="3">
-        <v>7074500</v>
+        <v>7872800</v>
       </c>
       <c r="K23" s="3">
         <v>6600500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2384000</v>
+        <v>2653000</v>
       </c>
       <c r="E24" s="3">
-        <v>1800100</v>
+        <v>2003300</v>
       </c>
       <c r="F24" s="3">
-        <v>1368700</v>
+        <v>1523200</v>
       </c>
       <c r="G24" s="3">
-        <v>997500</v>
+        <v>1110100</v>
       </c>
       <c r="H24" s="3">
-        <v>1069800</v>
+        <v>1190600</v>
       </c>
       <c r="I24" s="3">
-        <v>2114500</v>
+        <v>2353100</v>
       </c>
       <c r="J24" s="3">
-        <v>1725900</v>
+        <v>1920700</v>
       </c>
       <c r="K24" s="3">
         <v>1152200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6180200</v>
+        <v>6877700</v>
       </c>
       <c r="E26" s="3">
-        <v>5208100</v>
+        <v>5795900</v>
       </c>
       <c r="F26" s="3">
-        <v>4562000</v>
+        <v>5076900</v>
       </c>
       <c r="G26" s="3">
-        <v>3291400</v>
+        <v>3662800</v>
       </c>
       <c r="H26" s="3">
-        <v>4599700</v>
+        <v>5118800</v>
       </c>
       <c r="I26" s="3">
-        <v>5053900</v>
+        <v>5624300</v>
       </c>
       <c r="J26" s="3">
-        <v>5348500</v>
+        <v>5952100</v>
       </c>
       <c r="K26" s="3">
         <v>5448300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6143600</v>
+        <v>6836900</v>
       </c>
       <c r="E27" s="3">
-        <v>5141300</v>
+        <v>5721500</v>
       </c>
       <c r="F27" s="3">
-        <v>4508300</v>
+        <v>5017100</v>
       </c>
       <c r="G27" s="3">
-        <v>3271700</v>
+        <v>3641000</v>
       </c>
       <c r="H27" s="3">
-        <v>4490800</v>
+        <v>4997600</v>
       </c>
       <c r="I27" s="3">
-        <v>4636200</v>
+        <v>5159400</v>
       </c>
       <c r="J27" s="3">
-        <v>4685300</v>
+        <v>5214000</v>
       </c>
       <c r="K27" s="3">
         <v>4761900</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2787100</v>
+        <v>2081300</v>
       </c>
       <c r="E32" s="3">
-        <v>2850700</v>
+        <v>3172400</v>
       </c>
       <c r="F32" s="3">
-        <v>2248100</v>
+        <v>2501800</v>
       </c>
       <c r="G32" s="3">
-        <v>2070600</v>
+        <v>2304300</v>
       </c>
       <c r="H32" s="3">
-        <v>1432200</v>
+        <v>1593900</v>
       </c>
       <c r="I32" s="3">
-        <v>760500</v>
+        <v>846300</v>
       </c>
       <c r="J32" s="3">
-        <v>1262900</v>
+        <v>1405400</v>
       </c>
       <c r="K32" s="3">
         <v>1548300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6143600</v>
+        <v>6836900</v>
       </c>
       <c r="E33" s="3">
-        <v>5141300</v>
+        <v>5721500</v>
       </c>
       <c r="F33" s="3">
-        <v>4508300</v>
+        <v>5017100</v>
       </c>
       <c r="G33" s="3">
-        <v>3271700</v>
+        <v>3641000</v>
       </c>
       <c r="H33" s="3">
-        <v>4490800</v>
+        <v>4997600</v>
       </c>
       <c r="I33" s="3">
-        <v>4636200</v>
+        <v>5159400</v>
       </c>
       <c r="J33" s="3">
-        <v>4685300</v>
+        <v>5214000</v>
       </c>
       <c r="K33" s="3">
         <v>4761900</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6143600</v>
+        <v>6836900</v>
       </c>
       <c r="E35" s="3">
-        <v>5141300</v>
+        <v>5721500</v>
       </c>
       <c r="F35" s="3">
-        <v>4508300</v>
+        <v>5017100</v>
       </c>
       <c r="G35" s="3">
-        <v>3271700</v>
+        <v>3641000</v>
       </c>
       <c r="H35" s="3">
-        <v>4490800</v>
+        <v>4997600</v>
       </c>
       <c r="I35" s="3">
-        <v>4636200</v>
+        <v>5159400</v>
       </c>
       <c r="J35" s="3">
-        <v>4685300</v>
+        <v>5214000</v>
       </c>
       <c r="K35" s="3">
         <v>4761900</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>498553000</v>
+        <v>554816000</v>
       </c>
       <c r="E41" s="3">
-        <v>484331000</v>
+        <v>538989000</v>
       </c>
       <c r="F41" s="3">
-        <v>477174000</v>
+        <v>531024000</v>
       </c>
       <c r="G41" s="3">
-        <v>462989000</v>
+        <v>515239000</v>
       </c>
       <c r="H41" s="3">
-        <v>394084000</v>
+        <v>438557000</v>
       </c>
       <c r="I41" s="3">
-        <v>366284000</v>
+        <v>407620000</v>
       </c>
       <c r="J41" s="3">
-        <v>342814000</v>
+        <v>381501000</v>
       </c>
       <c r="K41" s="3">
         <v>315874000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>257568000</v>
+        <v>286635000</v>
       </c>
       <c r="E42" s="3">
-        <v>212452000</v>
+        <v>236427000</v>
       </c>
       <c r="F42" s="3">
-        <v>186198000</v>
+        <v>207211000</v>
       </c>
       <c r="G42" s="3">
-        <v>174772000</v>
+        <v>194495000</v>
       </c>
       <c r="H42" s="3">
-        <v>182721000</v>
+        <v>203341000</v>
       </c>
       <c r="I42" s="3">
-        <v>157174000</v>
+        <v>174911000</v>
       </c>
       <c r="J42" s="3">
-        <v>150122000</v>
+        <v>167063000</v>
       </c>
       <c r="K42" s="3">
         <v>164672000</v>
@@ -2262,26 +2262,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>5</v>
+      <c r="D47" s="3">
+        <v>12528000</v>
       </c>
       <c r="E47" s="3">
-        <v>8604300</v>
+        <v>9575300</v>
       </c>
       <c r="F47" s="3">
-        <v>7572900</v>
+        <v>8427500</v>
       </c>
       <c r="G47" s="3">
-        <v>6135500</v>
+        <v>6827900</v>
       </c>
       <c r="H47" s="3">
-        <v>6026800</v>
+        <v>6707000</v>
       </c>
       <c r="I47" s="3">
-        <v>6225900</v>
+        <v>6928500</v>
       </c>
       <c r="J47" s="3">
-        <v>4358500</v>
+        <v>4850400</v>
       </c>
       <c r="K47" s="3">
         <v>4074700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6423900</v>
+        <v>7148900</v>
       </c>
       <c r="E48" s="3">
-        <v>9535100</v>
+        <v>10611100</v>
       </c>
       <c r="F48" s="3">
-        <v>9297300</v>
+        <v>10346500</v>
       </c>
       <c r="G48" s="3">
-        <v>9308400</v>
+        <v>10358800</v>
       </c>
       <c r="H48" s="3">
-        <v>9253100</v>
+        <v>10297300</v>
       </c>
       <c r="I48" s="3">
-        <v>9600000</v>
+        <v>10683400</v>
       </c>
       <c r="J48" s="3">
-        <v>22171300</v>
+        <v>24673400</v>
       </c>
       <c r="K48" s="3">
         <v>20905100</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6231400</v>
+        <v>6934600</v>
       </c>
       <c r="E49" s="3">
-        <v>5728300</v>
+        <v>6374700</v>
       </c>
       <c r="F49" s="3">
-        <v>5734500</v>
+        <v>6381600</v>
       </c>
       <c r="G49" s="3">
-        <v>4713300</v>
+        <v>5245200</v>
       </c>
       <c r="H49" s="3">
-        <v>4807800</v>
+        <v>5350400</v>
       </c>
       <c r="I49" s="3">
-        <v>4907700</v>
+        <v>5461500</v>
       </c>
       <c r="J49" s="3">
-        <v>5522400</v>
+        <v>6145600</v>
       </c>
       <c r="K49" s="3">
         <v>6379500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6285700</v>
+        <v>6995000</v>
       </c>
       <c r="E52" s="3">
-        <v>4968300</v>
+        <v>5529000</v>
       </c>
       <c r="F52" s="3">
-        <v>4400700</v>
+        <v>4897300</v>
       </c>
       <c r="G52" s="3">
-        <v>3798500</v>
+        <v>4227200</v>
       </c>
       <c r="H52" s="3">
-        <v>1638900</v>
+        <v>1823900</v>
       </c>
       <c r="I52" s="3">
-        <v>2358600</v>
+        <v>2624700</v>
       </c>
       <c r="J52" s="3">
-        <v>2622400</v>
+        <v>2918300</v>
       </c>
       <c r="K52" s="3">
         <v>2547200</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1883610000</v>
+        <v>2096180000</v>
       </c>
       <c r="E54" s="3">
-        <v>1725330000</v>
+        <v>1920040000</v>
       </c>
       <c r="F54" s="3">
-        <v>1644160000</v>
+        <v>1829700000</v>
       </c>
       <c r="G54" s="3">
-        <v>1547690000</v>
+        <v>1722350000</v>
       </c>
       <c r="H54" s="3">
-        <v>1402730000</v>
+        <v>1561030000</v>
       </c>
       <c r="I54" s="3">
-        <v>1299350000</v>
+        <v>1445980000</v>
       </c>
       <c r="J54" s="3">
-        <v>1269930000</v>
+        <v>1413250000</v>
       </c>
       <c r="K54" s="3">
         <v>1333120000</v>
@@ -2705,20 +2705,20 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>5</v>
+      <c r="D58" s="3">
+        <v>226647000</v>
       </c>
       <c r="E58" s="3">
-        <v>175612000</v>
+        <v>195431000</v>
       </c>
       <c r="F58" s="3">
-        <v>178944000</v>
+        <v>199138000</v>
       </c>
       <c r="G58" s="3">
-        <v>162208000</v>
+        <v>180514000</v>
       </c>
       <c r="H58" s="3">
-        <v>155878000</v>
+        <v>173469000</v>
       </c>
       <c r="I58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>765000</v>
+        <v>851300</v>
       </c>
       <c r="E59" s="3">
-        <v>635200</v>
+        <v>706900</v>
       </c>
       <c r="F59" s="3">
-        <v>599500</v>
+        <v>667100</v>
       </c>
       <c r="G59" s="3">
-        <v>599300</v>
+        <v>666900</v>
       </c>
       <c r="H59" s="3">
-        <v>492700</v>
+        <v>548300</v>
       </c>
       <c r="I59" s="3">
-        <v>468600</v>
+        <v>521400</v>
       </c>
       <c r="J59" s="3">
-        <v>560800</v>
+        <v>624100</v>
       </c>
       <c r="K59" s="3">
         <v>542000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>177527000</v>
+        <v>197798000</v>
       </c>
       <c r="E61" s="3">
-        <v>153501000</v>
+        <v>170824000</v>
       </c>
       <c r="F61" s="3">
-        <v>183152000</v>
+        <v>203821000</v>
       </c>
       <c r="G61" s="3">
-        <v>170625000</v>
+        <v>189880000</v>
       </c>
       <c r="H61" s="3">
-        <v>156108000</v>
+        <v>173725000</v>
       </c>
       <c r="I61" s="3">
-        <v>126862000</v>
+        <v>141178000</v>
       </c>
       <c r="J61" s="3">
-        <v>126879000</v>
+        <v>141197000</v>
       </c>
       <c r="K61" s="3">
         <v>127494000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>5970500</v>
+        <v>6644300</v>
       </c>
       <c r="E62" s="3">
-        <v>3200700</v>
+        <v>3561900</v>
       </c>
       <c r="F62" s="3">
-        <v>3295100</v>
+        <v>3666900</v>
       </c>
       <c r="G62" s="3">
-        <v>4960500</v>
+        <v>5520300</v>
       </c>
       <c r="H62" s="3">
-        <v>3201700</v>
+        <v>3563100</v>
       </c>
       <c r="I62" s="3">
-        <v>3981100</v>
+        <v>4430400</v>
       </c>
       <c r="J62" s="3">
-        <v>4561400</v>
+        <v>5076100</v>
       </c>
       <c r="K62" s="3">
         <v>4210400</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1790070000</v>
+        <v>1992090000</v>
       </c>
       <c r="E66" s="3">
-        <v>1644430000</v>
+        <v>1830000000</v>
       </c>
       <c r="F66" s="3">
-        <v>1566960000</v>
+        <v>1743800000</v>
       </c>
       <c r="G66" s="3">
-        <v>1472220000</v>
+        <v>1638370000</v>
       </c>
       <c r="H66" s="3">
-        <v>1334320000</v>
+        <v>1484900000</v>
       </c>
       <c r="I66" s="3">
-        <v>1230610000</v>
+        <v>1369490000</v>
       </c>
       <c r="J66" s="3">
-        <v>1203620000</v>
+        <v>1339460000</v>
       </c>
       <c r="K66" s="3">
         <v>1267500000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>50047300</v>
+        <v>55695200</v>
       </c>
       <c r="E72" s="3">
-        <v>47369900</v>
+        <v>52715700</v>
       </c>
       <c r="F72" s="3">
-        <v>44136500</v>
+        <v>49117400</v>
       </c>
       <c r="G72" s="3">
-        <v>41434100</v>
+        <v>46110100</v>
       </c>
       <c r="H72" s="3">
-        <v>40438800</v>
+        <v>45002500</v>
       </c>
       <c r="I72" s="3">
-        <v>38260800</v>
+        <v>42578700</v>
       </c>
       <c r="J72" s="3">
-        <v>35443400</v>
+        <v>39443300</v>
       </c>
       <c r="K72" s="3">
         <v>33971200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>93537400</v>
+        <v>104093000</v>
       </c>
       <c r="E76" s="3">
-        <v>80908700</v>
+        <v>90039400</v>
       </c>
       <c r="F76" s="3">
-        <v>77196000</v>
+        <v>85907800</v>
       </c>
       <c r="G76" s="3">
-        <v>75464000</v>
+        <v>83980300</v>
       </c>
       <c r="H76" s="3">
-        <v>68406600</v>
+        <v>76126400</v>
       </c>
       <c r="I76" s="3">
-        <v>68732200</v>
+        <v>76488800</v>
       </c>
       <c r="J76" s="3">
-        <v>66309200</v>
+        <v>73792300</v>
       </c>
       <c r="K76" s="3">
         <v>65614000</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6143600</v>
+        <v>6836900</v>
       </c>
       <c r="E81" s="3">
-        <v>5141300</v>
+        <v>5721500</v>
       </c>
       <c r="F81" s="3">
-        <v>4508300</v>
+        <v>5017100</v>
       </c>
       <c r="G81" s="3">
-        <v>3271700</v>
+        <v>3641000</v>
       </c>
       <c r="H81" s="3">
-        <v>4490800</v>
+        <v>4997600</v>
       </c>
       <c r="I81" s="3">
-        <v>4636200</v>
+        <v>5159400</v>
       </c>
       <c r="J81" s="3">
-        <v>4685300</v>
+        <v>5214000</v>
       </c>
       <c r="K81" s="3">
         <v>4761900</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1869800</v>
+        <v>2080800</v>
       </c>
       <c r="E83" s="3">
-        <v>1709400</v>
+        <v>1902300</v>
       </c>
       <c r="F83" s="3">
-        <v>1543400</v>
+        <v>1717600</v>
       </c>
       <c r="G83" s="3">
-        <v>1449400</v>
+        <v>1613000</v>
       </c>
       <c r="H83" s="3">
-        <v>1446500</v>
+        <v>1609800</v>
       </c>
       <c r="I83" s="3">
-        <v>1881600</v>
+        <v>2094000</v>
       </c>
       <c r="J83" s="3">
-        <v>1957100</v>
+        <v>2178000</v>
       </c>
       <c r="K83" s="3">
         <v>2050700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4101500</v>
+        <v>4564300</v>
       </c>
       <c r="E89" s="3">
-        <v>-37611300</v>
+        <v>-41855800</v>
       </c>
       <c r="F89" s="3">
-        <v>9859800</v>
+        <v>10972500</v>
       </c>
       <c r="G89" s="3">
-        <v>119918200</v>
+        <v>133451300</v>
       </c>
       <c r="H89" s="3">
-        <v>45218500</v>
+        <v>50321500</v>
       </c>
       <c r="I89" s="3">
-        <v>29333700</v>
+        <v>32644100</v>
       </c>
       <c r="J89" s="3">
-        <v>59617000</v>
+        <v>66345000</v>
       </c>
       <c r="K89" s="3">
         <v>30446700</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-904000</v>
+        <v>-1006000</v>
       </c>
       <c r="E91" s="3">
-        <v>-638100</v>
+        <v>-710100</v>
       </c>
       <c r="F91" s="3">
-        <v>-590700</v>
+        <v>-657400</v>
       </c>
       <c r="G91" s="3">
-        <v>-931100</v>
+        <v>-1036200</v>
       </c>
       <c r="H91" s="3">
-        <v>-657500</v>
+        <v>-731700</v>
       </c>
       <c r="I91" s="3">
-        <v>-3255200</v>
+        <v>-3622500</v>
       </c>
       <c r="J91" s="3">
-        <v>-4546200</v>
+        <v>-5059200</v>
       </c>
       <c r="K91" s="3">
         <v>-3341800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-5862600</v>
+        <v>-6524200</v>
       </c>
       <c r="E94" s="3">
-        <v>37840200</v>
+        <v>42110500</v>
       </c>
       <c r="F94" s="3">
-        <v>-15355400</v>
+        <v>-17088400</v>
       </c>
       <c r="G94" s="3">
-        <v>-48997600</v>
+        <v>-54527100</v>
       </c>
       <c r="H94" s="3">
-        <v>-19214400</v>
+        <v>-21382800</v>
       </c>
       <c r="I94" s="3">
-        <v>6419900</v>
+        <v>7144400</v>
       </c>
       <c r="J94" s="3">
-        <v>-21662000</v>
+        <v>-24106600</v>
       </c>
       <c r="K94" s="3">
         <v>3918300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2220300</v>
+        <v>-2470900</v>
       </c>
       <c r="E96" s="3">
-        <v>-1924200</v>
+        <v>-2141400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1748500</v>
+        <v>-1945800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1704200</v>
+        <v>-1896500</v>
       </c>
       <c r="H96" s="3">
-        <v>-1631800</v>
+        <v>-1816000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1566900</v>
+        <v>-1743700</v>
       </c>
       <c r="J96" s="3">
-        <v>-1394500</v>
+        <v>-1551800</v>
       </c>
       <c r="K96" s="3">
         <v>-1382200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1790800</v>
+        <v>1992900</v>
       </c>
       <c r="E100" s="3">
-        <v>-2282600</v>
+        <v>-2540200</v>
       </c>
       <c r="F100" s="3">
-        <v>-3096500</v>
+        <v>-3445900</v>
       </c>
       <c r="G100" s="3">
-        <v>-3589300</v>
+        <v>-3994300</v>
       </c>
       <c r="H100" s="3">
-        <v>-6536700</v>
+        <v>-7274300</v>
       </c>
       <c r="I100" s="3">
-        <v>-4037400</v>
+        <v>-4493000</v>
       </c>
       <c r="J100" s="3">
-        <v>-2236000</v>
+        <v>-2488300</v>
       </c>
       <c r="K100" s="3">
         <v>-1122400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3262900</v>
+        <v>3631200</v>
       </c>
       <c r="E101" s="3">
-        <v>2259000</v>
+        <v>2514000</v>
       </c>
       <c r="F101" s="3">
-        <v>2345200</v>
+        <v>2609800</v>
       </c>
       <c r="G101" s="3">
-        <v>1020200</v>
+        <v>1135400</v>
       </c>
       <c r="H101" s="3">
-        <v>-475200</v>
+        <v>-528800</v>
       </c>
       <c r="I101" s="3">
-        <v>1063200</v>
+        <v>1183200</v>
       </c>
       <c r="J101" s="3">
-        <v>-598900</v>
+        <v>-666500</v>
       </c>
       <c r="K101" s="3">
         <v>-71100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3292600</v>
+        <v>3664200</v>
       </c>
       <c r="E102" s="3">
-        <v>205300</v>
+        <v>228400</v>
       </c>
       <c r="F102" s="3">
-        <v>-6246900</v>
+        <v>-6951900</v>
       </c>
       <c r="G102" s="3">
-        <v>68351500</v>
+        <v>76065200</v>
       </c>
       <c r="H102" s="3">
-        <v>18992300</v>
+        <v>21135600</v>
       </c>
       <c r="I102" s="3">
-        <v>32779500</v>
+        <v>36478700</v>
       </c>
       <c r="J102" s="3">
-        <v>35120100</v>
+        <v>39083500</v>
       </c>
       <c r="K102" s="3">
         <v>33171500</v>

--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>44116000</v>
+        <v>23502300</v>
       </c>
       <c r="E8" s="3">
-        <v>26836000</v>
+        <v>26840000</v>
       </c>
       <c r="F8" s="3">
-        <v>13546800</v>
+        <v>23147300</v>
       </c>
       <c r="G8" s="3">
-        <v>13156600</v>
+        <v>25911200</v>
       </c>
       <c r="H8" s="3">
-        <v>17440200</v>
+        <v>20865300</v>
       </c>
       <c r="I8" s="3">
-        <v>17671200</v>
+        <v>26062900</v>
       </c>
       <c r="J8" s="3">
-        <v>15377100</v>
+        <v>30828400</v>
       </c>
       <c r="K8" s="3">
         <v>12887100</v>
@@ -815,26 +815,26 @@
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>23502300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>26840000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>23147300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>25911200</v>
+      </c>
+      <c r="H10" s="3">
+        <v>20865300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>26062900</v>
+      </c>
+      <c r="J10" s="3">
+        <v>30828400</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>92400</v>
       </c>
       <c r="E14" s="3">
-        <v>0</v>
+        <v>1257300</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>836800</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>482800</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
+        <v>804900</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>894200</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>609600</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1014,26 +1014,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>5</v>
+      <c r="D15" s="3">
+        <v>621100</v>
       </c>
       <c r="E15" s="3">
-        <v>-1388300</v>
+        <v>679400</v>
       </c>
       <c r="F15" s="3">
-        <v>-1380800</v>
+        <v>2645100</v>
       </c>
       <c r="G15" s="3">
-        <v>-1293900</v>
+        <v>2803800</v>
       </c>
       <c r="H15" s="3">
-        <v>-1283400</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>5</v>
+        <v>2946700</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1975600</v>
+      </c>
+      <c r="J15" s="3">
+        <v>2920600</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>5</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>32504100</v>
+        <v>16485000</v>
       </c>
       <c r="E17" s="3">
-        <v>15864500</v>
+        <v>16747900</v>
       </c>
       <c r="F17" s="3">
-        <v>4444900</v>
+        <v>16650600</v>
       </c>
       <c r="G17" s="3">
-        <v>6079500</v>
+        <v>17109100</v>
       </c>
       <c r="H17" s="3">
-        <v>9537000</v>
+        <v>17656100</v>
       </c>
       <c r="I17" s="3">
-        <v>8847600</v>
+        <v>18023700</v>
       </c>
       <c r="J17" s="3">
-        <v>6098900</v>
+        <v>20147100</v>
       </c>
       <c r="K17" s="3">
         <v>4738300</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11611900</v>
+        <v>7017300</v>
       </c>
       <c r="E18" s="3">
-        <v>10971500</v>
+        <v>10092100</v>
       </c>
       <c r="F18" s="3">
-        <v>9101900</v>
+        <v>6496700</v>
       </c>
       <c r="G18" s="3">
-        <v>7077100</v>
+        <v>8802100</v>
       </c>
       <c r="H18" s="3">
-        <v>7903200</v>
+        <v>3209300</v>
       </c>
       <c r="I18" s="3">
-        <v>8823700</v>
+        <v>8039200</v>
       </c>
       <c r="J18" s="3">
-        <v>9278300</v>
+        <v>10681200</v>
       </c>
       <c r="K18" s="3">
         <v>8148800</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-2081300</v>
+        <v>-1060300</v>
       </c>
       <c r="E20" s="3">
-        <v>-3172400</v>
+        <v>-657700</v>
       </c>
       <c r="F20" s="3">
-        <v>-2501800</v>
+        <v>89300</v>
       </c>
       <c r="G20" s="3">
-        <v>-2304300</v>
+        <v>-328900</v>
       </c>
       <c r="H20" s="3">
-        <v>-1593900</v>
+        <v>-223300</v>
       </c>
       <c r="I20" s="3">
-        <v>-846300</v>
+        <v>-362400</v>
       </c>
       <c r="J20" s="3">
-        <v>-1405400</v>
+        <v>-464400</v>
       </c>
       <c r="K20" s="3">
         <v>-1548300</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>11596800</v>
+        <v>8698700</v>
       </c>
       <c r="E21" s="3">
-        <v>9688000</v>
+        <v>11429100</v>
       </c>
       <c r="F21" s="3">
-        <v>8305600</v>
+        <v>9052500</v>
       </c>
       <c r="G21" s="3">
-        <v>6374500</v>
+        <v>11934800</v>
       </c>
       <c r="H21" s="3">
-        <v>7907800</v>
+        <v>6379300</v>
       </c>
       <c r="I21" s="3">
-        <v>10056700</v>
+        <v>10377200</v>
       </c>
       <c r="J21" s="3">
-        <v>10035500</v>
+        <v>14066200</v>
       </c>
       <c r="K21" s="3">
         <v>8660400</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>9530700</v>
+        <v>7985100</v>
       </c>
       <c r="E23" s="3">
-        <v>7799200</v>
+        <v>9492500</v>
       </c>
       <c r="F23" s="3">
-        <v>6600100</v>
+        <v>5570600</v>
       </c>
       <c r="G23" s="3">
-        <v>4772900</v>
+        <v>8648200</v>
       </c>
       <c r="H23" s="3">
-        <v>6309400</v>
+        <v>2627700</v>
       </c>
       <c r="I23" s="3">
-        <v>7977400</v>
+        <v>7507400</v>
       </c>
       <c r="J23" s="3">
-        <v>7872800</v>
+        <v>10536000</v>
       </c>
       <c r="K23" s="3">
         <v>6600500</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>2653000</v>
+        <v>2063000</v>
       </c>
       <c r="E24" s="3">
-        <v>2003300</v>
+        <v>2452500</v>
       </c>
       <c r="F24" s="3">
-        <v>1523200</v>
+        <v>1329000</v>
       </c>
       <c r="G24" s="3">
-        <v>1110100</v>
+        <v>2273100</v>
       </c>
       <c r="H24" s="3">
-        <v>1190600</v>
+        <v>481100</v>
       </c>
       <c r="I24" s="3">
-        <v>2353100</v>
+        <v>1663300</v>
       </c>
       <c r="J24" s="3">
-        <v>1920700</v>
+        <v>2159800</v>
       </c>
       <c r="K24" s="3">
         <v>1152200</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>6877700</v>
+        <v>5922100</v>
       </c>
       <c r="E26" s="3">
-        <v>5795900</v>
+        <v>7040000</v>
       </c>
       <c r="F26" s="3">
-        <v>5076900</v>
+        <v>4241600</v>
       </c>
       <c r="G26" s="3">
-        <v>3662800</v>
+        <v>6375100</v>
       </c>
       <c r="H26" s="3">
-        <v>5118800</v>
+        <v>2146600</v>
       </c>
       <c r="I26" s="3">
-        <v>5624300</v>
+        <v>5844100</v>
       </c>
       <c r="J26" s="3">
-        <v>5952100</v>
+        <v>8376200</v>
       </c>
       <c r="K26" s="3">
         <v>5448300</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>6836900</v>
+        <v>5774000</v>
       </c>
       <c r="E27" s="3">
-        <v>5721500</v>
+        <v>6859300</v>
       </c>
       <c r="F27" s="3">
-        <v>5017100</v>
+        <v>4113900</v>
       </c>
       <c r="G27" s="3">
-        <v>3641000</v>
+        <v>6216000</v>
       </c>
       <c r="H27" s="3">
-        <v>4997600</v>
+        <v>1859200</v>
       </c>
       <c r="I27" s="3">
-        <v>5159400</v>
+        <v>4890600</v>
       </c>
       <c r="J27" s="3">
-        <v>5214000</v>
+        <v>7155900</v>
       </c>
       <c r="K27" s="3">
         <v>4761900</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>2081300</v>
+        <v>1060300</v>
       </c>
       <c r="E32" s="3">
-        <v>3172400</v>
+        <v>657700</v>
       </c>
       <c r="F32" s="3">
-        <v>2501800</v>
+        <v>-89300</v>
       </c>
       <c r="G32" s="3">
-        <v>2304300</v>
+        <v>328900</v>
       </c>
       <c r="H32" s="3">
-        <v>1593900</v>
+        <v>223300</v>
       </c>
       <c r="I32" s="3">
-        <v>846300</v>
+        <v>362400</v>
       </c>
       <c r="J32" s="3">
-        <v>1405400</v>
+        <v>464400</v>
       </c>
       <c r="K32" s="3">
         <v>1548300</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>6836900</v>
+        <v>5865000</v>
       </c>
       <c r="E33" s="3">
-        <v>5721500</v>
+        <v>6944400</v>
       </c>
       <c r="F33" s="3">
-        <v>5017100</v>
+        <v>4202300</v>
       </c>
       <c r="G33" s="3">
-        <v>3641000</v>
+        <v>6334600</v>
       </c>
       <c r="H33" s="3">
-        <v>4997600</v>
+        <v>1974100</v>
       </c>
       <c r="I33" s="3">
-        <v>5159400</v>
+        <v>4997800</v>
       </c>
       <c r="J33" s="3">
-        <v>5214000</v>
+        <v>7247500</v>
       </c>
       <c r="K33" s="3">
         <v>4761900</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>6836900</v>
+        <v>5865000</v>
       </c>
       <c r="E35" s="3">
-        <v>5721500</v>
+        <v>6944400</v>
       </c>
       <c r="F35" s="3">
-        <v>5017100</v>
+        <v>4202300</v>
       </c>
       <c r="G35" s="3">
-        <v>3641000</v>
+        <v>6334600</v>
       </c>
       <c r="H35" s="3">
-        <v>4997600</v>
+        <v>1974100</v>
       </c>
       <c r="I35" s="3">
-        <v>5159400</v>
+        <v>4997800</v>
       </c>
       <c r="J35" s="3">
-        <v>5214000</v>
+        <v>7247500</v>
       </c>
       <c r="K35" s="3">
         <v>4761900</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>554816000</v>
+        <v>498713000</v>
       </c>
       <c r="E41" s="3">
-        <v>538989000</v>
+        <v>550748900</v>
       </c>
       <c r="F41" s="3">
-        <v>531024000</v>
+        <v>594505200</v>
       </c>
       <c r="G41" s="3">
-        <v>515239000</v>
+        <v>629818900</v>
       </c>
       <c r="H41" s="3">
-        <v>438557000</v>
+        <v>552104400</v>
       </c>
       <c r="I41" s="3">
-        <v>407620000</v>
+        <v>495290400</v>
       </c>
       <c r="J41" s="3">
-        <v>381501000</v>
+        <v>486604000</v>
       </c>
       <c r="K41" s="3">
         <v>315874000</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>286635000</v>
+        <v>191656400</v>
       </c>
       <c r="E42" s="3">
-        <v>236427000</v>
+        <v>171137600</v>
       </c>
       <c r="F42" s="3">
-        <v>207211000</v>
+        <v>168849300</v>
       </c>
       <c r="G42" s="3">
-        <v>194495000</v>
+        <v>180629900</v>
       </c>
       <c r="H42" s="3">
-        <v>203341000</v>
+        <v>204998100</v>
       </c>
       <c r="I42" s="3">
-        <v>174911000</v>
+        <v>139258100</v>
       </c>
       <c r="J42" s="3">
-        <v>167063000</v>
+        <v>135756600</v>
       </c>
       <c r="K42" s="3">
         <v>164672000</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>16873500</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>7577300</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>12766600</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>12007200</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>12854200</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>11758300</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>11896400</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -2127,26 +2127,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>24958700</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>24726300</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>22819600</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>21344300</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>22673300</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>23372400</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>80885200</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>765808600</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>793910300</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>838972800</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>879653400</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>829638300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>700809500</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>746511900</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12528000</v>
+        <v>225245500</v>
       </c>
       <c r="E47" s="3">
-        <v>9575300</v>
+        <v>227335200</v>
       </c>
       <c r="F47" s="3">
-        <v>8427500</v>
+        <v>291923100</v>
       </c>
       <c r="G47" s="3">
-        <v>6827900</v>
+        <v>304513200</v>
       </c>
       <c r="H47" s="3">
-        <v>6707000</v>
+        <v>221768500</v>
       </c>
       <c r="I47" s="3">
-        <v>6928500</v>
+        <v>181503800</v>
       </c>
       <c r="J47" s="3">
-        <v>4850400</v>
+        <v>196685300</v>
       </c>
       <c r="K47" s="3">
         <v>4074700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7148900</v>
+        <v>8906100</v>
       </c>
       <c r="E48" s="3">
-        <v>10611100</v>
+        <v>13783100</v>
       </c>
       <c r="F48" s="3">
-        <v>10346500</v>
+        <v>14518100</v>
       </c>
       <c r="G48" s="3">
-        <v>10358800</v>
+        <v>15865100</v>
       </c>
       <c r="H48" s="3">
-        <v>10297300</v>
+        <v>16399400</v>
       </c>
       <c r="I48" s="3">
-        <v>10683400</v>
+        <v>13606900</v>
       </c>
       <c r="J48" s="3">
-        <v>24673400</v>
+        <v>14219000</v>
       </c>
       <c r="K48" s="3">
         <v>20905100</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6934600</v>
+        <v>6780300</v>
       </c>
       <c r="E49" s="3">
-        <v>6374700</v>
+        <v>6808100</v>
       </c>
       <c r="F49" s="3">
-        <v>6381600</v>
+        <v>8176000</v>
       </c>
       <c r="G49" s="3">
-        <v>5245200</v>
+        <v>7411600</v>
       </c>
       <c r="H49" s="3">
-        <v>5350400</v>
+        <v>7764500</v>
       </c>
       <c r="I49" s="3">
-        <v>5461500</v>
+        <v>7416200</v>
       </c>
       <c r="J49" s="3">
-        <v>6145600</v>
+        <v>7870600</v>
       </c>
       <c r="K49" s="3">
         <v>6379500</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6995000</v>
+        <v>12470900</v>
       </c>
       <c r="E52" s="3">
-        <v>5529000</v>
+        <v>11658100</v>
       </c>
       <c r="F52" s="3">
-        <v>4897300</v>
+        <v>11659500</v>
       </c>
       <c r="G52" s="3">
-        <v>4227200</v>
+        <v>10719800</v>
       </c>
       <c r="H52" s="3">
-        <v>1823900</v>
+        <v>6994600</v>
       </c>
       <c r="I52" s="3">
-        <v>2624700</v>
+        <v>20026600</v>
       </c>
       <c r="J52" s="3">
-        <v>2918300</v>
+        <v>24734100</v>
       </c>
       <c r="K52" s="3">
         <v>2547200</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2096180000</v>
+        <v>1859585700</v>
       </c>
       <c r="E54" s="3">
-        <v>1920040000</v>
+        <v>1938458500</v>
       </c>
       <c r="F54" s="3">
-        <v>1829700000</v>
+        <v>2043586200</v>
       </c>
       <c r="G54" s="3">
-        <v>1722350000</v>
+        <v>2125019100</v>
       </c>
       <c r="H54" s="3">
-        <v>1561030000</v>
+        <v>1971696300</v>
       </c>
       <c r="I54" s="3">
-        <v>1445980000</v>
+        <v>1764313900</v>
       </c>
       <c r="J54" s="3">
-        <v>1413250000</v>
+        <v>1809477600</v>
       </c>
       <c r="K54" s="3">
         <v>1333120000</v>
@@ -2660,26 +2660,26 @@
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="D57" s="3">
-        <v>0</v>
-      </c>
-      <c r="E57" s="3">
-        <v>0</v>
-      </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>226647000</v>
+        <v>306827000</v>
       </c>
       <c r="E58" s="3">
-        <v>195431000</v>
+        <v>290158800</v>
       </c>
       <c r="F58" s="3">
-        <v>199138000</v>
+        <v>344188400</v>
       </c>
       <c r="G58" s="3">
-        <v>180514000</v>
+        <v>338466400</v>
       </c>
       <c r="H58" s="3">
-        <v>173469000</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>5</v>
+        <v>362316300</v>
+      </c>
+      <c r="I58" s="3">
+        <v>194585100</v>
+      </c>
+      <c r="J58" s="3">
+        <v>198449300</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>5</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>851300</v>
+        <v>42475500</v>
       </c>
       <c r="E59" s="3">
-        <v>706900</v>
+        <v>33107100</v>
       </c>
       <c r="F59" s="3">
-        <v>667100</v>
+        <v>33915800</v>
       </c>
       <c r="G59" s="3">
-        <v>666900</v>
+        <v>26022500</v>
       </c>
       <c r="H59" s="3">
-        <v>548300</v>
+        <v>25117300</v>
       </c>
       <c r="I59" s="3">
-        <v>521400</v>
+        <v>25715900</v>
       </c>
       <c r="J59" s="3">
-        <v>624100</v>
+        <v>60796000</v>
       </c>
       <c r="K59" s="3">
         <v>542000</v>
@@ -2795,26 +2795,26 @@
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="D60" s="3">
-        <v>0</v>
-      </c>
-      <c r="E60" s="3">
-        <v>0</v>
-      </c>
-      <c r="F60" s="3">
-        <v>0</v>
-      </c>
-      <c r="G60" s="3">
-        <v>0</v>
-      </c>
-      <c r="H60" s="3">
-        <v>0</v>
-      </c>
-      <c r="I60" s="3">
-        <v>0</v>
-      </c>
-      <c r="J60" s="3">
-        <v>0</v>
+      <c r="D60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>197798000</v>
+        <v>139050600</v>
       </c>
       <c r="E61" s="3">
-        <v>170824000</v>
+        <v>166494600</v>
       </c>
       <c r="F61" s="3">
-        <v>203821000</v>
+        <v>174409800</v>
       </c>
       <c r="G61" s="3">
-        <v>189880000</v>
+        <v>185333400</v>
       </c>
       <c r="H61" s="3">
-        <v>173725000</v>
+        <v>146441500</v>
       </c>
       <c r="I61" s="3">
-        <v>141178000</v>
+        <v>188070300</v>
       </c>
       <c r="J61" s="3">
-        <v>141197000</v>
+        <v>176558400</v>
       </c>
       <c r="K61" s="3">
         <v>127494000</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>6644300</v>
+        <v>28095000</v>
       </c>
       <c r="E62" s="3">
-        <v>3561900</v>
+        <v>28219100</v>
       </c>
       <c r="F62" s="3">
-        <v>3666900</v>
+        <v>28057900</v>
       </c>
       <c r="G62" s="3">
-        <v>5520300</v>
+        <v>27814000</v>
       </c>
       <c r="H62" s="3">
-        <v>3563100</v>
+        <v>28515100</v>
       </c>
       <c r="I62" s="3">
-        <v>4430400</v>
+        <v>22128600</v>
       </c>
       <c r="J62" s="3">
-        <v>5076100</v>
+        <v>21792300</v>
       </c>
       <c r="K62" s="3">
         <v>4210400</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1992090000</v>
+        <v>1751958900</v>
       </c>
       <c r="E66" s="3">
-        <v>1830000000</v>
+        <v>1836626200</v>
       </c>
       <c r="F66" s="3">
-        <v>1743800000</v>
+        <v>1938329900</v>
       </c>
       <c r="G66" s="3">
-        <v>1638370000</v>
+        <v>2014022200</v>
       </c>
       <c r="H66" s="3">
-        <v>1484900000</v>
+        <v>1870072900</v>
       </c>
       <c r="I66" s="3">
-        <v>1369490000</v>
+        <v>1658064900</v>
       </c>
       <c r="J66" s="3">
-        <v>1339460000</v>
+        <v>1691820200</v>
       </c>
       <c r="K66" s="3">
         <v>1267500000</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>55695200</v>
+        <v>51365100</v>
       </c>
       <c r="E72" s="3">
-        <v>52715700</v>
+        <v>54158300</v>
       </c>
       <c r="F72" s="3">
-        <v>49117400</v>
+        <v>52988500</v>
       </c>
       <c r="G72" s="3">
-        <v>46110100</v>
+        <v>54957200</v>
       </c>
       <c r="H72" s="3">
-        <v>45002500</v>
+        <v>52135200</v>
       </c>
       <c r="I72" s="3">
-        <v>42578700</v>
+        <v>51575700</v>
       </c>
       <c r="J72" s="3">
-        <v>39443300</v>
+        <v>48483500</v>
       </c>
       <c r="K72" s="3">
         <v>33971200</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>104093000</v>
+        <v>106720700</v>
       </c>
       <c r="E76" s="3">
-        <v>90039400</v>
+        <v>101033500</v>
       </c>
       <c r="F76" s="3">
-        <v>85907800</v>
+        <v>104487800</v>
       </c>
       <c r="G76" s="3">
-        <v>83980300</v>
+        <v>110378700</v>
       </c>
       <c r="H76" s="3">
-        <v>76126400</v>
+        <v>101063000</v>
       </c>
       <c r="I76" s="3">
-        <v>76488800</v>
+        <v>101789800</v>
       </c>
       <c r="J76" s="3">
-        <v>73792300</v>
+        <v>106047900</v>
       </c>
       <c r="K76" s="3">
         <v>65614000</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>6836900</v>
+        <v>5865000</v>
       </c>
       <c r="E81" s="3">
-        <v>5721500</v>
+        <v>6944400</v>
       </c>
       <c r="F81" s="3">
-        <v>5017100</v>
+        <v>4202300</v>
       </c>
       <c r="G81" s="3">
-        <v>3641000</v>
+        <v>6334600</v>
       </c>
       <c r="H81" s="3">
-        <v>4997600</v>
+        <v>1974100</v>
       </c>
       <c r="I81" s="3">
-        <v>5159400</v>
+        <v>4997800</v>
       </c>
       <c r="J81" s="3">
-        <v>5214000</v>
+        <v>7247500</v>
       </c>
       <c r="K81" s="3">
         <v>4761900</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>2080800</v>
+        <v>1027300</v>
       </c>
       <c r="E83" s="3">
-        <v>1902300</v>
+        <v>1161600</v>
       </c>
       <c r="F83" s="3">
-        <v>1717600</v>
+        <v>2645100</v>
       </c>
       <c r="G83" s="3">
-        <v>1613000</v>
+        <v>2803800</v>
       </c>
       <c r="H83" s="3">
-        <v>1609800</v>
+        <v>2946700</v>
       </c>
       <c r="I83" s="3">
-        <v>2094000</v>
+        <v>1975600</v>
       </c>
       <c r="J83" s="3">
-        <v>2178000</v>
+        <v>2920600</v>
       </c>
       <c r="K83" s="3">
         <v>2050700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>4564300</v>
+        <v>-45517200</v>
       </c>
       <c r="E89" s="3">
-        <v>-41855800</v>
+        <v>-111444300</v>
       </c>
       <c r="F89" s="3">
-        <v>10972500</v>
+        <v>-8206300</v>
       </c>
       <c r="G89" s="3">
-        <v>133451300</v>
+        <v>14596900</v>
       </c>
       <c r="H89" s="3">
-        <v>50321500</v>
+        <v>41896000</v>
       </c>
       <c r="I89" s="3">
-        <v>32644100</v>
+        <v>-21150400</v>
       </c>
       <c r="J89" s="3">
-        <v>66345000</v>
+        <v>49818300</v>
       </c>
       <c r="K89" s="3">
         <v>30446700</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1006000</v>
+        <v>-791400</v>
       </c>
       <c r="E91" s="3">
-        <v>-710100</v>
+        <v>-661900</v>
       </c>
       <c r="F91" s="3">
-        <v>-657400</v>
+        <v>-670100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1036200</v>
+        <v>-1009400</v>
       </c>
       <c r="H91" s="3">
-        <v>-731700</v>
+        <v>-780200</v>
       </c>
       <c r="I91" s="3">
-        <v>-3622500</v>
+        <v>-4592000</v>
       </c>
       <c r="J91" s="3">
-        <v>-5059200</v>
+        <v>-6693100</v>
       </c>
       <c r="K91" s="3">
         <v>-3341800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-6524200</v>
+        <v>-5398500</v>
       </c>
       <c r="E94" s="3">
-        <v>42110500</v>
+        <v>43625100</v>
       </c>
       <c r="F94" s="3">
-        <v>-17088400</v>
+        <v>-21932800</v>
       </c>
       <c r="G94" s="3">
-        <v>-54527100</v>
+        <v>-70352000</v>
       </c>
       <c r="H94" s="3">
-        <v>-21382800</v>
+        <v>-27812900</v>
       </c>
       <c r="I94" s="3">
-        <v>7144400</v>
+        <v>10843500</v>
       </c>
       <c r="J94" s="3">
-        <v>-24106600</v>
+        <v>-33837200</v>
       </c>
       <c r="K94" s="3">
         <v>3918300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2470900</v>
+        <v>2391800</v>
       </c>
       <c r="E96" s="3">
-        <v>-2141400</v>
+        <v>2353900</v>
       </c>
       <c r="F96" s="3">
-        <v>-1945800</v>
+        <v>2345200</v>
       </c>
       <c r="G96" s="3">
-        <v>-1896500</v>
+        <v>2533800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1816000</v>
+        <v>2491900</v>
       </c>
       <c r="I96" s="3">
-        <v>-1743700</v>
+        <v>2323500</v>
       </c>
       <c r="J96" s="3">
-        <v>-1551800</v>
+        <v>2149500</v>
       </c>
       <c r="K96" s="3">
         <v>-1382200</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>1992900</v>
+        <v>53469500</v>
       </c>
       <c r="E100" s="3">
-        <v>-2540200</v>
+        <v>68570000</v>
       </c>
       <c r="F100" s="3">
-        <v>-3445900</v>
+        <v>45290900</v>
       </c>
       <c r="G100" s="3">
-        <v>-3994300</v>
+        <v>144879600</v>
       </c>
       <c r="H100" s="3">
-        <v>-7274300</v>
+        <v>30143600</v>
       </c>
       <c r="I100" s="3">
-        <v>-4493000</v>
+        <v>39690700</v>
       </c>
       <c r="J100" s="3">
-        <v>-2488300</v>
+        <v>51977100</v>
       </c>
       <c r="K100" s="3">
         <v>-1122400</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>3631200</v>
+        <v>11287600</v>
       </c>
       <c r="E101" s="3">
-        <v>2514000</v>
+        <v>6773800</v>
       </c>
       <c r="F101" s="3">
-        <v>2609800</v>
+        <v>7866900</v>
       </c>
       <c r="G101" s="3">
-        <v>1135400</v>
+        <v>4413000</v>
       </c>
       <c r="H101" s="3">
-        <v>-528800</v>
+        <v>-2526700</v>
       </c>
       <c r="I101" s="3">
-        <v>1183200</v>
+        <v>397600</v>
       </c>
       <c r="J101" s="3">
-        <v>-666500</v>
+        <v>-431900</v>
       </c>
       <c r="K101" s="3">
         <v>-71100</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>3664200</v>
+        <v>13841300</v>
       </c>
       <c r="E102" s="3">
-        <v>228400</v>
+        <v>7524700</v>
       </c>
       <c r="F102" s="3">
-        <v>-6951900</v>
+        <v>23018700</v>
       </c>
       <c r="G102" s="3">
-        <v>76065200</v>
+        <v>93537500</v>
       </c>
       <c r="H102" s="3">
-        <v>21135600</v>
+        <v>41700100</v>
       </c>
       <c r="I102" s="3">
-        <v>36478700</v>
+        <v>29781400</v>
       </c>
       <c r="J102" s="3">
-        <v>39083500</v>
+        <v>67526400</v>
       </c>
       <c r="K102" s="3">
         <v>33171500</v>

--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -656,117 +656,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>34857300</v>
+      </c>
+      <c r="E8" s="3">
         <v>23502300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>26840000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23147300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25911200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>20865300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>26062900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>30828400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>12887100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>13732100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>16138200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16534000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>15686800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>15461400</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -809,36 +815,39 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>34857300</v>
+      </c>
+      <c r="E10" s="3">
         <v>23502300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>26840000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>23147300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>25911200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>20865300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>26062900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>30828400</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -854,9 +863,12 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,36 +979,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E14" s="3">
         <v>92400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>1257300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>836800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>482800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>804900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>894200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>609600</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
@@ -1008,36 +1027,39 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="E15" s="3">
         <v>621100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>679400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2645100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2803800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2946700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1975600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2920600</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L15" s="3" t="s">
         <v>5</v>
       </c>
@@ -1047,15 +1069,18 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3">
         <v>-1185200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>-1099400</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>23453300</v>
+      </c>
+      <c r="E17" s="3">
         <v>16485000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>16747900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>16650600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17109100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17656100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18023700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>20147100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>4738300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3929800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3297800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2380800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2923100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2835200</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>11404000</v>
+      </c>
+      <c r="E18" s="3">
         <v>7017300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>10092100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>6496700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>8802100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>3209300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>8039200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>10681200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>8148800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>9802300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>12840400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14153200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12763800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12626200</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,98 +1211,105 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1060300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-657700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>89300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-328900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-223300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-362400</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-464400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1548300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2598000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1671400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1121300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4503500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4386900</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13279000</v>
+      </c>
+      <c r="E21" s="3">
         <v>8698700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11429100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>9052500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11934800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6379300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10377200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>14066200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>8660400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9140900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>13315400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>15152100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>10302300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>9804500</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1295,8 +1334,8 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L22" s="3">
         <v>0</v>
@@ -1313,99 +1352,108 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>11352000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7985100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>9492500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>5570600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>8648200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>2627700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>7507400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>10536000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6600500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>7204200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>11169000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>13031900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>8260200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>8239300</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3426200</v>
+      </c>
+      <c r="E24" s="3">
         <v>2063000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>2452500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1329000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2273100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>481100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1663300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2159800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1152200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1654100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3764800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>4202700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2319400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4162400</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>7925800</v>
+      </c>
+      <c r="E26" s="3">
         <v>5922100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>7040000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4241600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>6375100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2146600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>5844100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>8376200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>5448300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>5550200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7404200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>8829200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>5940900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>4076900</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>7866500</v>
+      </c>
+      <c r="E27" s="3">
         <v>5774000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>6859300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4113900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>6216000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1859200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>4890600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>7155900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4761900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4753100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>6428300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>7651900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>3743300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>3058400</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3">
         <v>1060300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>657700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-89300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>328900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>223300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>362400</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>464400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1548300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2598000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1671400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1121300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4503500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4386900</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>7866500</v>
+      </c>
+      <c r="E33" s="3">
         <v>5865000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>6944400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4202300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>6334600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1974100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>4997800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>7247500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>4761900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>4753100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>6428300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>7651900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>3743300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>3058400</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>7866500</v>
+      </c>
+      <c r="E35" s="3">
         <v>5865000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>6944400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4202300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>6334600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1974100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>4997800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>7247500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>4761900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>4753100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>6428300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>7651900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>3743300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>3058400</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,125 +2072,132 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>441993700</v>
+      </c>
+      <c r="E41" s="3">
         <v>498713000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>550748900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>594505200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>629818900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>552104400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>495290400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>486604000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>315874000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>314501000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>339059000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>302199000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>217778000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>84465200</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>226927600</v>
+      </c>
+      <c r="E42" s="3">
         <v>191656400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>171137600</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>168849300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>180629900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>204998100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>139258100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>135756600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>164672000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>174560000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>189608000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>163523000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>183032000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>39736300</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>62791500</v>
+      </c>
+      <c r="E43" s="3">
         <v>16873500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7577300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>12766600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>12007200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>12854200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>11758300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>11896400</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -2121,9 +2213,12 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2148,8 +2243,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2166,36 +2261,39 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>119216100</v>
+      </c>
+      <c r="E45" s="3">
         <v>24958700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>24726300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22819600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>21344300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22673300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23372400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>80885200</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
       <c r="L45" s="3">
         <v>0</v>
       </c>
@@ -2211,36 +2309,39 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>851144500</v>
+      </c>
+      <c r="E46" s="3">
         <v>765808600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>793910300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>838972800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>879653400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>829638300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>700809500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>746511900</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -2256,144 +2357,156 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>309720000</v>
+      </c>
+      <c r="E47" s="3">
         <v>225245500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>227335200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>291923100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>304513200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>221768500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>181503800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>196685300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4074700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4486600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4979100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3411000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4711900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1868200</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>6721700</v>
+      </c>
+      <c r="E48" s="3">
         <v>8906100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>13783100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>14518100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>15865100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16399400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>13606900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>14219000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>20905100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>21457800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23635400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>21496600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>36213000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>20247600</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>6793600</v>
+      </c>
+      <c r="E49" s="3">
         <v>6780300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6808100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>8176000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>7411600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>7764500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>7416200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>7870600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>6379500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>6455200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>6990800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>7510200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>15399600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16256900</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>98233400</v>
+      </c>
+      <c r="E52" s="3">
         <v>12470900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>11658100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>11659500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>10719800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>6994600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>20026600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>24734100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2547200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2418900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>4299900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2684900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7796700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8355100</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2045316200</v>
+      </c>
+      <c r="E54" s="3">
         <v>1859585700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1938458500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2043586200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2125019100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1971696300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1764313900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1809477600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1333120000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1371410000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1564770000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1479660000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1343090000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1281880000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,8 +2784,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2681,8 +2811,8 @@
       <c r="J57" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
+      <c r="K57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L57" s="3">
         <v>0</v>
@@ -2699,38 +2829,41 @@
       <c r="P57" s="3">
         <v>0</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3">
+        <v>0</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>202029300</v>
+      </c>
+      <c r="E58" s="3">
         <v>306827000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>290158800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>344188400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>338466400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>362316300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>194585100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>198449300</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
+      <c r="L58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M58" s="3">
         <v>0</v>
@@ -2744,54 +2877,60 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>166055100</v>
+      </c>
+      <c r="E59" s="3">
         <v>42475500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>33107100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>33915800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>26022500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>25117300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>25715900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>60796000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>542000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>521300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>654300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>681000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4547000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>2359800</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2816,8 +2955,8 @@
       <c r="J60" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
+      <c r="K60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L60" s="3">
         <v>0</v>
@@ -2834,99 +2973,108 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>208814400</v>
+      </c>
+      <c r="E61" s="3">
         <v>139050600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>166494600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>174409800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>185333400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>146441500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>188070300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>176558400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>127494000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>115272000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>137357000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>110944000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>58862700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>94132200</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>105228600</v>
+      </c>
+      <c r="E62" s="3">
         <v>28095000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28219100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28057900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27814000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28515100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22128600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21792300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4210400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5131000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>7540600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3803400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6030000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1152100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1946206300</v>
+      </c>
+      <c r="E66" s="3">
         <v>1751958900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1836626200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1938329900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2014022200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1870072900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1658064900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1691820200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1267500000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1305870000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1487790000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1412960000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1284350000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1233310000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>55360800</v>
+      </c>
+      <c r="E72" s="3">
         <v>51365100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>54158300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>52988500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>54957200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>52135200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>51575700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>48483500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>33971200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>33349600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>34979000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>31894000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>57285400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>21765900</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>98193000</v>
+      </c>
+      <c r="E76" s="3">
         <v>106720700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>101033500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>104487800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>110378700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>101063000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>101789800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>106047900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>65614000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>65537400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>76979300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>66693800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58740700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>48567700</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>7866500</v>
+      </c>
+      <c r="E81" s="3">
         <v>5865000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>6944400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4202300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>6334600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1974100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>4997800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>7247500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>4761900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>4753100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>6428300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>7651900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>3743300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>3058400</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1655200</v>
+      </c>
+      <c r="E83" s="3">
         <v>1027300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1161600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2645100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2803800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2946700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1975600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2920600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2050700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1955200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>2121500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2111000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2037600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1563500</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28648500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-45517200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-111444300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8206300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>14596900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41896000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-21150400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>49818300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>30446700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-8285300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>69840100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>76062400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21574500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>11941900</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-740800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-791400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-661900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-670100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1009400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-780200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4592000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6693100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3341800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3890100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4938600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4260700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5273500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1175100</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-30136900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-5398500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>43625100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-21932800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-70352000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-27812900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>10843500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-33837200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>3918300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>38521000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12429800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>133008000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>12797800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-22347400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,53 +4453,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>2752100</v>
+      </c>
+      <c r="E96" s="3">
         <v>2391800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2353900</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>2345200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>2533800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>2491900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>2323500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2149500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1382200</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1557800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1457900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1557000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2458000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1283000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>58627400</v>
+      </c>
+      <c r="E100" s="3">
         <v>53469500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>68570000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>45290900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>144879600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>30143600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39690700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>51977100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1122400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-411600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2581100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-9515500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6725300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-2759000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-1128500</v>
+      </c>
+      <c r="E101" s="3">
         <v>11287600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>6773800</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7866900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4413000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-2526700</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>397600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-431900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-71100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-731900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1515800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>51100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>5676200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-557600</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1286500</v>
+      </c>
+      <c r="E102" s="3">
         <v>13841300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7524700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>23018700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>93537500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>41700100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>29781400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>67526400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33171500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>29092200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>56345100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>199606000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>33323200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-13722100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SMFG_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
   <si>
     <t>SMFG</t>
   </si>
@@ -729,13 +729,13 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>34857300</v>
+        <v>21868000</v>
       </c>
       <c r="E8" s="3">
-        <v>23502300</v>
+        <v>23465200</v>
       </c>
       <c r="F8" s="3">
-        <v>26840000</v>
+        <v>26836000</v>
       </c>
       <c r="G8" s="3">
         <v>23147300</v>
@@ -825,13 +825,13 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>34857300</v>
+        <v>21868000</v>
       </c>
       <c r="E10" s="3">
-        <v>23502300</v>
+        <v>23465200</v>
       </c>
       <c r="F10" s="3">
-        <v>26840000</v>
+        <v>26836000</v>
       </c>
       <c r="G10" s="3">
         <v>23147300</v>
@@ -989,13 +989,13 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>52000</v>
+        <v>154100</v>
       </c>
       <c r="E14" s="3">
         <v>92400</v>
       </c>
       <c r="F14" s="3">
-        <v>1257300</v>
+        <v>2206300</v>
       </c>
       <c r="G14" s="3">
         <v>836800</v>
@@ -1037,13 +1037,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1875000</v>
+        <v>523700</v>
       </c>
       <c r="E15" s="3">
         <v>621100</v>
       </c>
       <c r="F15" s="3">
-        <v>679400</v>
+        <v>2424800</v>
       </c>
       <c r="G15" s="3">
         <v>2645100</v>
@@ -1102,13 +1102,13 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>23453300</v>
+        <v>18297700</v>
       </c>
       <c r="E17" s="3">
-        <v>16485000</v>
+        <v>16447900</v>
       </c>
       <c r="F17" s="3">
-        <v>16747900</v>
+        <v>15794900</v>
       </c>
       <c r="G17" s="3">
         <v>16650600</v>
@@ -1150,13 +1150,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>11404000</v>
+        <v>3570300</v>
       </c>
       <c r="E18" s="3">
         <v>7017300</v>
       </c>
       <c r="F18" s="3">
-        <v>10092100</v>
+        <v>11041100</v>
       </c>
       <c r="G18" s="3">
         <v>6496700</v>
@@ -1217,8 +1217,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>5</v>
+      <c r="D20" s="3">
+        <v>-952800</v>
       </c>
       <c r="E20" s="3">
         <v>-1060300</v>
@@ -1266,13 +1266,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13279000</v>
+        <v>5046800</v>
       </c>
       <c r="E21" s="3">
         <v>8698700</v>
       </c>
       <c r="F21" s="3">
-        <v>11429100</v>
+        <v>14123600</v>
       </c>
       <c r="G21" s="3">
         <v>9052500</v>
@@ -1362,7 +1362,7 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>11352000</v>
+        <v>4369000</v>
       </c>
       <c r="E23" s="3">
         <v>7985100</v>
@@ -1410,7 +1410,7 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>3426200</v>
+        <v>920200</v>
       </c>
       <c r="E24" s="3">
         <v>2063000</v>
@@ -1506,7 +1506,7 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>7925800</v>
+        <v>3448800</v>
       </c>
       <c r="E26" s="3">
         <v>5922100</v>
@@ -1554,7 +1554,7 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>7866500</v>
+        <v>3192900</v>
       </c>
       <c r="E27" s="3">
         <v>5774000</v>
@@ -1793,8 +1793,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>5</v>
+      <c r="D32" s="3">
+        <v>952800</v>
       </c>
       <c r="E32" s="3">
         <v>1060300</v>
@@ -1842,7 +1842,7 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>7866500</v>
+        <v>3404200</v>
       </c>
       <c r="E33" s="3">
         <v>5865000</v>
@@ -1938,7 +1938,7 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>7866500</v>
+        <v>3404200</v>
       </c>
       <c r="E35" s="3">
         <v>5865000</v>
@@ -2079,7 +2079,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>441993700</v>
+        <v>487471200</v>
       </c>
       <c r="E41" s="3">
         <v>498713000</v>
@@ -2127,7 +2127,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>226927600</v>
+        <v>233004900</v>
       </c>
       <c r="E42" s="3">
         <v>191656400</v>
@@ -2175,7 +2175,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>62791500</v>
+        <v>22262600</v>
       </c>
       <c r="E43" s="3">
         <v>16873500</v>
@@ -2271,7 +2271,7 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>119216100</v>
+        <v>27049200</v>
       </c>
       <c r="E45" s="3">
         <v>24958700</v>
@@ -2319,7 +2319,7 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>851144500</v>
+        <v>798281200</v>
       </c>
       <c r="E46" s="3">
         <v>765808600</v>
@@ -2367,7 +2367,7 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>309720000</v>
+        <v>253970300</v>
       </c>
       <c r="E47" s="3">
         <v>225245500</v>
@@ -2415,7 +2415,7 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6721700</v>
+        <v>8808100</v>
       </c>
       <c r="E48" s="3">
         <v>8906100</v>
@@ -2463,7 +2463,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>6793600</v>
+        <v>7286900</v>
       </c>
       <c r="E49" s="3">
         <v>6780300</v>
@@ -2607,7 +2607,7 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>98233400</v>
+        <v>11536200</v>
       </c>
       <c r="E52" s="3">
         <v>12470900</v>
@@ -2703,7 +2703,7 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>2045316200</v>
+        <v>1951044900</v>
       </c>
       <c r="E54" s="3">
         <v>1859585700</v>
@@ -2839,7 +2839,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>202029300</v>
+        <v>341151300</v>
       </c>
       <c r="E58" s="3">
         <v>306827000</v>
@@ -2887,7 +2887,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>166055100</v>
+        <v>43521100</v>
       </c>
       <c r="E59" s="3">
         <v>42475500</v>
@@ -2983,7 +2983,7 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>208814400</v>
+        <v>129177800</v>
       </c>
       <c r="E61" s="3">
         <v>139050600</v>
@@ -3031,7 +3031,7 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>105228600</v>
+        <v>29238900</v>
       </c>
       <c r="E62" s="3">
         <v>28095000</v>
@@ -3223,7 +3223,7 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1946206300</v>
+        <v>1840935900</v>
       </c>
       <c r="E66" s="3">
         <v>1751958900</v>
@@ -3483,7 +3483,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>55360800</v>
+        <v>52331600</v>
       </c>
       <c r="E72" s="3">
         <v>51365100</v>
@@ -3675,7 +3675,7 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>98193000</v>
+        <v>109107100</v>
       </c>
       <c r="E76" s="3">
         <v>106720700</v>
@@ -3824,7 +3824,7 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>7866500</v>
+        <v>3404200</v>
       </c>
       <c r="E81" s="3">
         <v>5865000</v>
@@ -3892,13 +3892,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1655200</v>
+        <v>927400</v>
       </c>
       <c r="E83" s="3">
         <v>1027300</v>
       </c>
       <c r="F83" s="3">
-        <v>1161600</v>
+        <v>2424800</v>
       </c>
       <c r="G83" s="3">
         <v>2645100</v>
@@ -4180,7 +4180,7 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-28648500</v>
+        <v>-33294900</v>
       </c>
       <c r="E89" s="3">
         <v>-45517200</v>
@@ -4248,7 +4248,7 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-740800</v>
+        <v>-657800</v>
       </c>
       <c r="E91" s="3">
         <v>-791400</v>
@@ -4392,7 +4392,7 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-30136900</v>
+        <v>-30256100</v>
       </c>
       <c r="E94" s="3">
         <v>-5398500</v>
@@ -4460,7 +4460,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>2752100</v>
+        <v>2963400</v>
       </c>
       <c r="E96" s="3">
         <v>2391800</v>
@@ -4652,7 +4652,7 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>58627400</v>
+        <v>49681300</v>
       </c>
       <c r="E100" s="3">
         <v>53469500</v>
@@ -4700,7 +4700,7 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-1128500</v>
+        <v>-739400</v>
       </c>
       <c r="E101" s="3">
         <v>11287600</v>
@@ -4748,7 +4748,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-1286500</v>
+        <v>-14609100</v>
       </c>
       <c r="E102" s="3">
         <v>13841300</v>
